--- a/tests/testthat/fixtures/example_corrupt.xlsx
+++ b/tests/testthat/fixtures/example_corrupt.xlsx
@@ -386,7 +386,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:A54"/>
+  <dimension ref="A1:A56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="100.711"/>
@@ -542,229 +542,243 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">  Advanced settings may be added as extra rows, e.g. cores, thin, adapt_delta,</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>observations sheet -- one row per sampled count:</t>
+          <t xml:space="preserve">  max_treedepth, df, or dose_schedule (the age each dose is given, e.g. 1, 4).</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Location          the location of this count (must match a Location in the locations sheet)</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Observation Year  timing of the observation</t>
+          <t>observations sheet -- one row per sampled count:</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Youngest age      youngest age this count covers</t>
+          <t xml:space="preserve">  Location          the location of this count (must match a Location in the locations sheet)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Oldest age        oldest age this count covers (put the same age in both for a single age)</t>
+          <t xml:space="preserve">  Observation Year  timing of the observation</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Dose              which dose this count is for: 1 or 2</t>
+          <t xml:space="preserve">  Youngest age      youngest age this count covers</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Vaccinated        how many were found vaccinated</t>
+          <t xml:space="preserve">  Oldest age        oldest age this count covers (for a single age, repeat it or leave blank)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Sampled           how many were sampled (Vaccinated must be &lt;= Sampled)</t>
+          <t xml:space="preserve">  Dose              which dose this count is for (1 = first dose, 2 = second, ...)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Censored          optional; leave blank, or put 1 for a right-censored observation</t>
+          <t xml:space="preserve">  Vaccinated        how many were found vaccinated</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  A count covering several ages is split evenly across them, and the cohort of each age</t>
+          <t xml:space="preserve">  Sampled           how many were sampled (Vaccinated must be &lt;= Sampled)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  is derived as Observation Year - age (a snapshot in time). If you prefer,</t>
+          <t xml:space="preserve">  Censored          optional; leave blank, or put 1 for a right-censored observation</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  you may use a single 'Age' column instead of the two age columns.</t>
+          <t xml:space="preserve">  A count covering several ages is split evenly across them, and the cohort of each age</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">  is derived as Observation Year - age (a snapshot in time). If you prefer,</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>locations sheet -- your location hierarchy, written as a tree:</t>
+          <t xml:space="preserve">  you may use a single 'Age' column instead of the two age columns.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Location          a unique name for the location (you choose the names)</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Parent location   the name of this location's parent (must be another Location in this sheet)</t>
+          <t>locations sheet -- your location hierarchy, written as a tree:</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  IMPORTANT: there must be exactly ONE root -- the single top location whose Parent location</t>
+          <t xml:space="preserve">  Location          a unique name for the location (you choose the names)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  is left BLANK. Every other location must name its parent, and the parents must chain up to</t>
+          <t xml:space="preserve">  Parent location   the name of this location's parent (must be another Location in this sheet)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  that one root (no loops, no second root). This is the most common thing to get wrong.</t>
+          <t xml:space="preserve">  IMPORTANT: there must be exactly ONE root -- the single top location whose Parent location</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">  is left BLANK. Every other location must name its parent, and the parents must chain up to</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>target sheet -- the populations to predict coverage for (required):</t>
+          <t xml:space="preserve">  that one root (no loops, no second root). This is the most common thing to get wrong.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Location          one or more locations to predict, ';'-separated</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Target Year       timing of the target snapshot to predict</t>
+          <t>target sheet -- the populations to predict coverage for (required):</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Youngest age      youngest age to predict</t>
+          <t xml:space="preserve">  Location          one or more locations to predict, ';'-separated</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Oldest age        oldest age to predict</t>
+          <t xml:space="preserve">  Target Year       timing of the target snapshot to predict</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Dose              optional; leave blank to default to the final dose</t>
+          <t xml:space="preserve">  Youngest age      youngest age to predict</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Label             optional; free-text label echoed into the results</t>
+          <t xml:space="preserve">  Oldest age        oldest age to predict</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  A Location-only row (year/ages/dose left blank) inherits those from the row above it.</t>
+          <t xml:space="preserve">  Dose              optional; leave blank to default to the final dose</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">  Label             optional; free-text label echoed into the results</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>Check from R: imuRUN::run_fit('yourfile.xlsx', dryrun = TRUE)</t>
+          <t xml:space="preserve">  A Location-only row (year/ages/dose left blank) inherits those from the row above it.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>Fit from R:   imuRUN::run_fit('yourfile.xlsx')</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>Check from R: imuRUN::run_fit('yourfile.xlsx', dryrun = TRUE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>Fit from R:   imuRUN::run_fit('yourfile.xlsx')</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
         <is>
           <t>If you installed the optional command wrapper, 'imurun yourfile.xlsx' also works.</t>
         </is>
@@ -966,7 +980,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="C3">
@@ -993,7 +1007,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="C4">
@@ -1020,7 +1034,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="C5">
@@ -1047,7 +1061,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="C6">
@@ -1074,7 +1088,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="C7">
@@ -1101,7 +1115,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="C8">
@@ -1128,7 +1142,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="C9">
@@ -1155,7 +1169,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="C10">
@@ -1182,7 +1196,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="C11">
@@ -1209,7 +1223,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="C12">
@@ -1236,7 +1250,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="C13">
@@ -1263,7 +1277,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="C14">
@@ -1290,7 +1304,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="C15">
@@ -1317,7 +1331,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="C16">
@@ -1344,7 +1358,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="C17">
@@ -1371,7 +1385,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="C18">
@@ -1398,7 +1412,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="C19">
@@ -1425,7 +1439,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="C20">
@@ -1452,7 +1466,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="C21">
@@ -1479,7 +1493,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="C22">
@@ -1506,7 +1520,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="C23">
@@ -1533,7 +1547,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="C24">
@@ -1560,7 +1574,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C25">
@@ -1587,7 +1601,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C26">
@@ -1614,7 +1628,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C27">
@@ -1641,7 +1655,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="C28">
@@ -1668,7 +1682,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="C29">
@@ -1695,7 +1709,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="C30">
@@ -1722,7 +1736,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="C31">
@@ -1749,7 +1763,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="C32">
@@ -1776,7 +1790,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="C33">
@@ -1803,7 +1817,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="C34">
@@ -1830,7 +1844,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="C35">
@@ -1857,7 +1871,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="C36">
@@ -1884,7 +1898,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="C37">
@@ -1911,7 +1925,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="C38">
@@ -1938,7 +1952,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="C39">
@@ -1965,7 +1979,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="C40">
@@ -1992,7 +2006,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="C41">
@@ -2019,7 +2033,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="C42">
@@ -2046,7 +2060,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="C43">
@@ -2073,7 +2087,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="C44">
@@ -2100,7 +2114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="C45">
@@ -2127,7 +2141,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="C46">
@@ -2154,7 +2168,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="C47">
@@ -2181,7 +2195,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="C48">
@@ -2208,7 +2222,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="C49">
@@ -2235,7 +2249,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="C50">
@@ -2262,7 +2276,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="C51">
@@ -2289,7 +2303,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="C52">
@@ -2316,7 +2330,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C53">
@@ -2343,7 +2357,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C54">
@@ -2370,7 +2384,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C55">
@@ -2397,7 +2411,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="C56">
@@ -2424,7 +2438,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="C57">
@@ -2451,7 +2465,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="C58">
@@ -2478,7 +2492,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="C59">
@@ -2505,7 +2519,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="C60">
@@ -2532,7 +2546,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="C61">
@@ -2559,7 +2573,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="C62">
@@ -2586,7 +2600,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="C63">
@@ -2613,7 +2627,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="C64">
@@ -2640,7 +2654,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="C65">
@@ -2667,7 +2681,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="C66">
@@ -2694,7 +2708,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="C67">
@@ -2721,7 +2735,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="C68">
@@ -2748,7 +2762,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="C69">
@@ -2775,7 +2789,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="C70">
@@ -2802,7 +2816,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="C71">
@@ -2829,7 +2843,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="C72">
@@ -2856,7 +2870,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="C73">
@@ -2883,7 +2897,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="C74">
@@ -2910,7 +2924,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="C75">
@@ -2937,7 +2951,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="C76">
@@ -2964,7 +2978,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="C77">
@@ -2991,7 +3005,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="C78">
@@ -3018,7 +3032,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="C79">
@@ -3045,7 +3059,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="C80">
@@ -3072,7 +3086,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C81">
@@ -3099,7 +3113,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C82">
@@ -3126,7 +3140,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C83">
@@ -3153,7 +3167,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="C84">
@@ -3180,7 +3194,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="C85">
@@ -3207,7 +3221,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="C86">
@@ -3234,7 +3248,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="C87">
@@ -3261,7 +3275,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="C88">
@@ -3288,7 +3302,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="C89">
@@ -3315,7 +3329,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="C90">
@@ -3342,7 +3356,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="C91">
@@ -3369,7 +3383,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="C92">
@@ -3396,7 +3410,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="C93">
@@ -3423,7 +3437,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="C94">
@@ -3450,7 +3464,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="C95">
@@ -3477,7 +3491,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="C96">
@@ -3504,7 +3518,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="C97">
@@ -3531,7 +3545,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="C98">
@@ -3558,7 +3572,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="C99">
@@ -3585,7 +3599,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="C100">
@@ -3612,7 +3626,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="C101">
@@ -3639,7 +3653,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="C102">
@@ -3666,7 +3680,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="C103">
@@ -3693,7 +3707,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="C104">
@@ -3720,7 +3734,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="C105">
@@ -3747,7 +3761,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="C106">
@@ -3774,7 +3788,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="C107">
@@ -3801,7 +3815,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="C108">
@@ -3828,7 +3842,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C109">
@@ -3855,7 +3869,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C110">
@@ -3882,7 +3896,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C111">
@@ -3909,7 +3923,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="C112">
@@ -3936,7 +3950,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="C113">
@@ -3963,7 +3977,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="C114">
@@ -3990,7 +4004,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="C115">
@@ -4017,7 +4031,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="C116">
@@ -4044,7 +4058,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="C117">
@@ -4071,7 +4085,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="C118">
@@ -4098,7 +4112,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="C119">
@@ -4125,7 +4139,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="C120">
@@ -4152,7 +4166,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="C121">
@@ -4179,7 +4193,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="C122">
@@ -4206,7 +4220,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="C123">
@@ -4233,7 +4247,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="C124">
@@ -4260,7 +4274,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="C125">
@@ -4287,7 +4301,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="C126">
@@ -4314,7 +4328,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="C127">
@@ -4341,7 +4355,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="C128">
@@ -4368,7 +4382,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="C129">
@@ -4395,7 +4409,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="C130">
@@ -4422,7 +4436,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="C131">
@@ -4449,7 +4463,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="C132">
@@ -4476,7 +4490,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="C133">
@@ -4503,7 +4517,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="C134">
@@ -4530,7 +4544,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="C135">
@@ -4557,7 +4571,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="C136">
@@ -4584,7 +4598,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C137">
@@ -4611,7 +4625,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C138">
@@ -4638,7 +4652,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C139">
@@ -4665,7 +4679,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="C140">
@@ -4692,7 +4706,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="C141">
@@ -4719,7 +4733,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="C142">
@@ -4746,7 +4760,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="C143">
@@ -4773,7 +4787,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="C144">
@@ -4800,7 +4814,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="C145">
@@ -4827,7 +4841,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="C146">
@@ -4854,7 +4868,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="C147">
@@ -4881,7 +4895,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="C148">
@@ -4908,7 +4922,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="C149">
@@ -4935,7 +4949,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="C150">
@@ -4962,7 +4976,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="C151">
@@ -4989,7 +5003,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="C152">
@@ -5016,7 +5030,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="C153">
@@ -5043,7 +5057,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="C154">
@@ -5070,7 +5084,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="C155">
@@ -5097,7 +5111,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="C156">
@@ -5124,7 +5138,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="C157">
@@ -5151,7 +5165,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="C158">
@@ -5178,7 +5192,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="C159">
@@ -5205,7 +5219,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="C160">
@@ -5232,7 +5246,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="C161">
@@ -5259,7 +5273,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="C162">
@@ -5286,7 +5300,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="C163">
@@ -5313,7 +5327,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="C164">
@@ -5340,7 +5354,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C165">
@@ -5367,7 +5381,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C166">
@@ -5394,7 +5408,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C167">
@@ -5421,7 +5435,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="C168">
@@ -5448,7 +5462,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="C169">
@@ -5475,7 +5489,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="C170">
@@ -5502,7 +5516,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="C171">
@@ -5529,7 +5543,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="C172">
@@ -5556,7 +5570,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="C173">
@@ -5583,7 +5597,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="C174">
@@ -5610,7 +5624,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="C175">
@@ -5637,7 +5651,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="C176">
@@ -5664,7 +5678,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="C177">
@@ -5691,7 +5705,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="C178">
@@ -5718,7 +5732,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="C179">
@@ -5745,7 +5759,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="C180">
@@ -5772,7 +5786,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="C181">
@@ -5799,7 +5813,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="C182">
@@ -5826,7 +5840,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="C183">
@@ -5853,7 +5867,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="C184">
@@ -5880,7 +5894,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="C185">
@@ -5907,7 +5921,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="C186">
@@ -5934,7 +5948,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="C187">
@@ -5961,7 +5975,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="C188">
@@ -5988,7 +6002,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="C189">
@@ -6015,7 +6029,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="C190">
@@ -6042,7 +6056,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="C191">
@@ -6069,7 +6083,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="C192">
@@ -6096,7 +6110,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C193">
@@ -6123,7 +6137,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C194">
@@ -6150,7 +6164,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C195">
@@ -6177,7 +6191,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="C196">
@@ -6204,7 +6218,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="C197">
@@ -6231,7 +6245,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="C198">
@@ -6258,7 +6272,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="C199">
@@ -6285,7 +6299,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="C200">
@@ -6312,7 +6326,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="C201">
@@ -6339,7 +6353,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="C202">
@@ -6366,7 +6380,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="C203">
@@ -6393,7 +6407,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="C204">
@@ -6420,7 +6434,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="C205">
@@ -6447,7 +6461,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="C206">
@@ -6474,7 +6488,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="C207">
@@ -6501,7 +6515,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="C208">
@@ -6528,7 +6542,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="C209">
@@ -6555,7 +6569,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="C210">
@@ -6582,7 +6596,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="C211">
@@ -6609,7 +6623,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="C212">
@@ -6636,7 +6650,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="C213">
@@ -6663,7 +6677,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="C214">
@@ -6690,7 +6704,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="C215">
@@ -6717,7 +6731,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="C216">
@@ -6744,7 +6758,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="C217">
@@ -6771,7 +6785,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="C218">
@@ -6798,7 +6812,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="C219">
@@ -6825,7 +6839,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="C220">
@@ -6852,7 +6866,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C221">
@@ -6879,7 +6893,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C222">
@@ -6906,7 +6920,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C223">
@@ -6933,7 +6947,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="C224">
@@ -6960,7 +6974,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="C225">
@@ -6987,7 +7001,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="C226">
@@ -7014,7 +7028,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="C227">
@@ -7041,7 +7055,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="C228">
@@ -7068,7 +7082,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="C229">
@@ -7095,7 +7109,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="C230">
@@ -7122,7 +7136,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="C231">
@@ -7149,7 +7163,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="C232">
@@ -7176,7 +7190,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="C233">
@@ -7203,7 +7217,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="C234">
@@ -7230,7 +7244,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="C235">
@@ -7257,7 +7271,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="C236">
@@ -7284,7 +7298,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="C237">
@@ -7311,7 +7325,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="C238">
@@ -7338,7 +7352,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="C239">
@@ -7365,7 +7379,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="C240">
@@ -7392,7 +7406,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="C241">
@@ -7419,7 +7433,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="C242">
@@ -7446,7 +7460,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="C243">
@@ -7473,7 +7487,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="C244">
@@ -7500,7 +7514,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="C245">
@@ -7527,7 +7541,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="C246">
@@ -7554,7 +7568,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="C247">
@@ -7581,7 +7595,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="C248">
@@ -7608,7 +7622,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C249">
@@ -7635,7 +7649,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C250">
@@ -7662,7 +7676,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C251">
@@ -7689,7 +7703,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="C252">
@@ -7716,7 +7730,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="C253">
@@ -7743,7 +7757,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="C254">
@@ -7770,7 +7784,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="C255">
@@ -7797,7 +7811,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="C256">
@@ -7824,7 +7838,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="C257">
@@ -7851,7 +7865,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="C258">
@@ -7878,7 +7892,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="C259">
@@ -7905,7 +7919,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="C260">
@@ -7932,7 +7946,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="C261">
@@ -7959,7 +7973,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="C262">
@@ -7986,7 +8000,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="C263">
@@ -8013,7 +8027,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="C264">
@@ -8040,7 +8054,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="C265">
@@ -8067,7 +8081,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="C266">
@@ -8094,7 +8108,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="C267">
@@ -8121,7 +8135,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="C268">
@@ -8148,7 +8162,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="C269">
@@ -8175,7 +8189,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="C270">
@@ -8202,7 +8216,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="C271">
@@ -8229,7 +8243,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="C272">
@@ -8256,7 +8270,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="C273">
@@ -8283,7 +8297,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="C274">
@@ -8310,7 +8324,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="C275">
@@ -8337,7 +8351,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="C276">
@@ -8364,7 +8378,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C277">
@@ -8391,7 +8405,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C278">
@@ -8418,7 +8432,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C279">
@@ -8445,7 +8459,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="C280">
@@ -8472,7 +8486,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="C281">
@@ -8499,7 +8513,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="C282">
@@ -8526,7 +8540,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="C283">
@@ -8553,7 +8567,7 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="C284">
@@ -8580,7 +8594,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="C285">
@@ -8607,7 +8621,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="C286">
@@ -8634,7 +8648,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="C287">
@@ -8661,7 +8675,7 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="C288">
@@ -8688,7 +8702,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="C289">
@@ -8715,7 +8729,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="C290">
@@ -8742,7 +8756,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="C291">
@@ -8769,7 +8783,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="C292">
@@ -8796,7 +8810,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="C293">
@@ -8823,7 +8837,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="C294">
@@ -8850,7 +8864,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="C295">
@@ -8877,7 +8891,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="C296">
@@ -8904,7 +8918,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="C297">
@@ -8931,7 +8945,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="C298">
@@ -8958,7 +8972,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="C299">
@@ -8985,7 +8999,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="C300">
@@ -9012,7 +9026,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="C301">
@@ -9039,7 +9053,7 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="C302">
@@ -9066,7 +9080,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="C303">
@@ -9093,7 +9107,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="C304">
@@ -9120,7 +9134,7 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C305">
@@ -9147,7 +9161,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C306">
@@ -9174,7 +9188,7 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C307">
@@ -9201,7 +9215,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="C308">
@@ -9228,7 +9242,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="C309">
@@ -9255,7 +9269,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="C310">
@@ -9282,7 +9296,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="C311">
@@ -9309,7 +9323,7 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="C312">
@@ -9336,7 +9350,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="C313">
@@ -9363,7 +9377,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="C314">
@@ -9390,7 +9404,7 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="C315">
@@ -9417,7 +9431,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="C316">
@@ -9444,7 +9458,7 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="C317">
@@ -9471,7 +9485,7 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="C318">
@@ -9498,7 +9512,7 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="C319">
@@ -9525,7 +9539,7 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="C320">
@@ -9552,7 +9566,7 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="C321">
@@ -9579,7 +9593,7 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="C322">
@@ -9606,7 +9620,7 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="C323">
@@ -9633,7 +9647,7 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="C324">
@@ -9660,7 +9674,7 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="C325">
@@ -9687,7 +9701,7 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="C326">
@@ -9714,7 +9728,7 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="C327">
@@ -9741,7 +9755,7 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="C328">
@@ -9768,7 +9782,7 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="C329">
@@ -9795,7 +9809,7 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="C330">
@@ -9822,7 +9836,7 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="C331">
@@ -9849,7 +9863,7 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="C332">
@@ -9876,7 +9890,7 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C333">
@@ -9903,7 +9917,7 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C334">
@@ -9930,7 +9944,7 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C335">
@@ -9957,7 +9971,7 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="C336">
@@ -9984,7 +9998,7 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="C337">
@@ -10011,7 +10025,7 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="C338">
@@ -10038,7 +10052,7 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="C339">
@@ -10065,7 +10079,7 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="C340">
@@ -10092,7 +10106,7 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="C341">
@@ -10119,7 +10133,7 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="C342">
@@ -10146,7 +10160,7 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="C343">
@@ -10173,7 +10187,7 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="C344">
@@ -10200,7 +10214,7 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="C345">
@@ -10227,7 +10241,7 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="C346">
@@ -10254,7 +10268,7 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="C347">
@@ -10281,7 +10295,7 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="C348">
@@ -10308,7 +10322,7 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="C349">
@@ -10335,7 +10349,7 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="C350">
@@ -10362,7 +10376,7 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="C351">
@@ -10389,7 +10403,7 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="C352">
@@ -10416,7 +10430,7 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="C353">
@@ -10443,7 +10457,7 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="C354">
@@ -10470,7 +10484,7 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="C355">
@@ -10497,7 +10511,7 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="C356">
@@ -10524,7 +10538,7 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="C357">
@@ -10551,7 +10565,7 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="C358">
@@ -10578,7 +10592,7 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="C359">
@@ -10605,7 +10619,7 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="C360">
@@ -10632,7 +10646,7 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C361">
@@ -10659,7 +10673,7 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C362">
@@ -10686,7 +10700,7 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C363">
@@ -10713,7 +10727,7 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="C364">
@@ -10740,7 +10754,7 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="C365">
@@ -10767,7 +10781,7 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="C366">
@@ -10794,7 +10808,7 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="C367">
@@ -10821,7 +10835,7 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="C368">
@@ -10848,7 +10862,7 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="C369">
@@ -10875,7 +10889,7 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="C370">
@@ -10902,7 +10916,7 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="C371">
@@ -10929,7 +10943,7 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="C372">
@@ -10956,7 +10970,7 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="C373">
@@ -10983,7 +10997,7 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="C374">
@@ -11010,7 +11024,7 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="C375">
@@ -11037,7 +11051,7 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="C376">
@@ -11064,7 +11078,7 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="C377">
@@ -11091,7 +11105,7 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="C378">
@@ -11118,7 +11132,7 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="C379">
@@ -11145,7 +11159,7 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="C380">
@@ -11172,7 +11186,7 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="C381">
@@ -11199,7 +11213,7 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="C382">
@@ -11226,7 +11240,7 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="C383">
@@ -11253,7 +11267,7 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="C384">
@@ -11280,7 +11294,7 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="C385">
@@ -11307,7 +11321,7 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="C386">
@@ -11334,7 +11348,7 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="C387">
@@ -11361,7 +11375,7 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="C388">
@@ -11388,7 +11402,7 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C389">
@@ -11415,7 +11429,7 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C390">
@@ -11442,7 +11456,7 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C391">
@@ -11469,7 +11483,7 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="C392">
@@ -11496,7 +11510,7 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="C393">
@@ -11523,7 +11537,7 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="C394">
@@ -11550,7 +11564,7 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="C395">
@@ -11577,7 +11591,7 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="C396">
@@ -11604,7 +11618,7 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="C397">
@@ -11631,7 +11645,7 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="C398">
@@ -11658,7 +11672,7 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="C399">
@@ -11685,7 +11699,7 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="C400">
@@ -11712,7 +11726,7 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="C401">
@@ -11739,7 +11753,7 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="C402">
@@ -11766,7 +11780,7 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="C403">
@@ -11793,7 +11807,7 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="C404">
@@ -11820,7 +11834,7 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="C405">
@@ -11847,7 +11861,7 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="C406">
@@ -11874,7 +11888,7 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="C407">
@@ -11901,7 +11915,7 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="C408">
@@ -11928,7 +11942,7 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="C409">
@@ -11955,7 +11969,7 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="C410">
@@ -11982,7 +11996,7 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="C411">
@@ -12009,7 +12023,7 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="C412">
@@ -12036,7 +12050,7 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="C413">
@@ -12063,7 +12077,7 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="C414">
@@ -12090,7 +12104,7 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="C415">
@@ -12117,7 +12131,7 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="C416">
@@ -12144,7 +12158,7 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C417">
@@ -12171,7 +12185,7 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C418">
@@ -12198,7 +12212,7 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C419">
@@ -12225,7 +12239,7 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="C420">
@@ -12252,7 +12266,7 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="C421">
@@ -12279,7 +12293,7 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="C422">
@@ -12306,7 +12320,7 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="C423">
@@ -12333,7 +12347,7 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="C424">
@@ -12360,7 +12374,7 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="C425">
@@ -12387,7 +12401,7 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="C426">
@@ -12414,7 +12428,7 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="C427">
@@ -12441,7 +12455,7 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="C428">
@@ -12468,7 +12482,7 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="C429">
@@ -12495,7 +12509,7 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="C430">
@@ -12522,7 +12536,7 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="C431">
@@ -12549,7 +12563,7 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="C432">
@@ -12576,7 +12590,7 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="C433">
@@ -12603,7 +12617,7 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="C434">
@@ -12630,7 +12644,7 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="C435">
@@ -12657,7 +12671,7 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="C436">
@@ -12684,7 +12698,7 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="C437">
@@ -12711,7 +12725,7 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="C438">
@@ -12738,7 +12752,7 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="C439">
@@ -12765,7 +12779,7 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="C440">
@@ -12792,7 +12806,7 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="C441">
@@ -12819,7 +12833,7 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="C442">
@@ -12846,7 +12860,7 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="C443">
@@ -12873,7 +12887,7 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="C444">
@@ -12900,7 +12914,7 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C445">
@@ -12927,7 +12941,7 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C446">
@@ -12954,7 +12968,7 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C447">
@@ -12981,7 +12995,7 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="C448">
@@ -13008,7 +13022,7 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="C449">
@@ -13035,7 +13049,7 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="C450">
@@ -13062,7 +13076,7 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="C451">
@@ -13089,7 +13103,7 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="C452">
@@ -13116,7 +13130,7 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="C453">
@@ -13143,7 +13157,7 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="C454">
@@ -13170,7 +13184,7 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="C455">
@@ -13197,7 +13211,7 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="C456">
@@ -13224,7 +13238,7 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="C457">
@@ -13251,7 +13265,7 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="C458">
@@ -13278,7 +13292,7 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="C459">
@@ -13305,7 +13319,7 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="C460">
@@ -13332,7 +13346,7 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="C461">
@@ -13359,7 +13373,7 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="C462">
@@ -13386,7 +13400,7 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="C463">
@@ -13413,7 +13427,7 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="C464">
@@ -13440,7 +13454,7 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="C465">
@@ -13467,7 +13481,7 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="C466">
@@ -13494,7 +13508,7 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="C467">
@@ -13521,7 +13535,7 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="C468">
@@ -13548,7 +13562,7 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="C469">
@@ -13575,7 +13589,7 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="C470">
@@ -13602,7 +13616,7 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="C471">
@@ -13629,7 +13643,7 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="C472">
@@ -13656,7 +13670,7 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C473">
@@ -13683,7 +13697,7 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C474">
@@ -13710,7 +13724,7 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C475">
@@ -13737,7 +13751,7 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="C476">
@@ -13764,7 +13778,7 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="C477">
@@ -13791,7 +13805,7 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="C478">
@@ -13818,7 +13832,7 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="C479">
@@ -13845,7 +13859,7 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="C480">
@@ -13872,7 +13886,7 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="C481">
@@ -13899,7 +13913,7 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="C482">
@@ -13926,7 +13940,7 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="C483">
@@ -13953,7 +13967,7 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="C484">
@@ -13980,7 +13994,7 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="C485">
@@ -14007,7 +14021,7 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="C486">
@@ -14034,7 +14048,7 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="C487">
@@ -14061,7 +14075,7 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="C488">
@@ -14088,7 +14102,7 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="C489">
@@ -14115,7 +14129,7 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="C490">
@@ -14142,7 +14156,7 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="C491">
@@ -14169,7 +14183,7 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="C492">
@@ -14196,7 +14210,7 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="C493">
@@ -14223,7 +14237,7 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="C494">
@@ -14250,7 +14264,7 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="C495">
@@ -14277,7 +14291,7 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="C496">
@@ -14304,7 +14318,7 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="C497">
@@ -14331,7 +14345,7 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="C498">
@@ -14358,7 +14372,7 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="C499">
@@ -14385,7 +14399,7 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="C500">
@@ -14412,7 +14426,7 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C501">
@@ -14439,7 +14453,7 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C502">
@@ -14466,7 +14480,7 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C503">
@@ -14493,7 +14507,7 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="C504">
@@ -14520,7 +14534,7 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="C505">
@@ -14547,7 +14561,7 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="C506">
@@ -14574,7 +14588,7 @@
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="C507">
@@ -14601,7 +14615,7 @@
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="C508">
@@ -14628,7 +14642,7 @@
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="C509">
@@ -14655,7 +14669,7 @@
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="C510">
@@ -14682,7 +14696,7 @@
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="C511">
@@ -14709,7 +14723,7 @@
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="C512">
@@ -14736,7 +14750,7 @@
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="C513">
@@ -14763,7 +14777,7 @@
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="C514">
@@ -14790,7 +14804,7 @@
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="C515">
@@ -14817,7 +14831,7 @@
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="C516">
@@ -14844,7 +14858,7 @@
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="C517">
@@ -14871,7 +14885,7 @@
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="C518">
@@ -14898,7 +14912,7 @@
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="C519">
@@ -14925,7 +14939,7 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="C520">
@@ -14952,7 +14966,7 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="C521">
@@ -14979,7 +14993,7 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="C522">
@@ -15006,7 +15020,7 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="C523">
@@ -15033,7 +15047,7 @@
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="C524">
@@ -15060,7 +15074,7 @@
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="C525">
@@ -15087,7 +15101,7 @@
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="C526">
@@ -15114,7 +15128,7 @@
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="C527">
@@ -15141,7 +15155,7 @@
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="C528">
@@ -15168,7 +15182,7 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C529">
@@ -15195,7 +15209,7 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C530">
@@ -15222,7 +15236,7 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C531">
@@ -15249,7 +15263,7 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="C532">
@@ -15276,7 +15290,7 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="C533">
@@ -15303,7 +15317,7 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="C534">
@@ -15330,7 +15344,7 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="C535">
@@ -15357,7 +15371,7 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="C536">
@@ -15384,7 +15398,7 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="C537">
@@ -15411,7 +15425,7 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="C538">
@@ -15438,7 +15452,7 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="C539">
@@ -15465,7 +15479,7 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="C540">
@@ -15492,7 +15506,7 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="C541">
@@ -15519,7 +15533,7 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="C542">
@@ -15546,7 +15560,7 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="C543">
@@ -15573,7 +15587,7 @@
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="C544">
@@ -15600,7 +15614,7 @@
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="C545">
@@ -15627,7 +15641,7 @@
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="C546">
@@ -15654,7 +15668,7 @@
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="C547">
@@ -15681,7 +15695,7 @@
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="C548">
@@ -15708,7 +15722,7 @@
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="C549">
@@ -15735,7 +15749,7 @@
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="C550">
@@ -15762,7 +15776,7 @@
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="C551">
@@ -15789,7 +15803,7 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="C552">
@@ -15816,7 +15830,7 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="C553">
@@ -15843,7 +15857,7 @@
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="C554">
@@ -15870,7 +15884,7 @@
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="C555">
@@ -15897,7 +15911,7 @@
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="C556">
@@ -15924,7 +15938,7 @@
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C557">
@@ -15951,7 +15965,7 @@
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C558">
@@ -15978,7 +15992,7 @@
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C559">
@@ -16005,7 +16019,7 @@
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="C560">
@@ -16032,7 +16046,7 @@
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="C561">
@@ -16059,7 +16073,7 @@
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="C562">
@@ -16086,7 +16100,7 @@
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="C563">
@@ -16113,7 +16127,7 @@
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="C564">
@@ -16140,7 +16154,7 @@
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="C565">
@@ -16167,7 +16181,7 @@
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="C566">
@@ -16194,7 +16208,7 @@
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="C567">
@@ -16221,7 +16235,7 @@
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="C568">
@@ -16248,7 +16262,7 @@
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="C569">
@@ -16275,7 +16289,7 @@
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="C570">
@@ -16302,7 +16316,7 @@
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="C571">
@@ -16329,7 +16343,7 @@
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="C572">
@@ -16356,7 +16370,7 @@
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="C573">
@@ -16383,7 +16397,7 @@
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="C574">
@@ -16410,7 +16424,7 @@
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="C575">
@@ -16437,7 +16451,7 @@
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="C576">
@@ -16464,7 +16478,7 @@
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="C577">
@@ -16491,7 +16505,7 @@
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="C578">
@@ -16518,7 +16532,7 @@
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="C579">
@@ -16545,7 +16559,7 @@
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="C580">
@@ -16572,7 +16586,7 @@
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="C581">
@@ -16599,7 +16613,7 @@
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="C582">
@@ -16626,7 +16640,7 @@
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="C583">
@@ -16653,7 +16667,7 @@
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="C584">
@@ -16680,7 +16694,7 @@
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C585">
@@ -16707,7 +16721,7 @@
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C586">
@@ -16734,7 +16748,7 @@
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C587">
@@ -16761,7 +16775,7 @@
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="C588">
@@ -16788,7 +16802,7 @@
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="C589">
@@ -16815,7 +16829,7 @@
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="C590">
@@ -16842,7 +16856,7 @@
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="C591">
@@ -16869,7 +16883,7 @@
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="C592">
@@ -16896,7 +16910,7 @@
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="C593">
@@ -16923,7 +16937,7 @@
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="C594">
@@ -16950,7 +16964,7 @@
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="C595">
@@ -16977,7 +16991,7 @@
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="C596">
@@ -17004,7 +17018,7 @@
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="C597">
@@ -17031,7 +17045,7 @@
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="C598">
@@ -17058,7 +17072,7 @@
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="C599">
@@ -17085,7 +17099,7 @@
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="C600">
@@ -17112,7 +17126,7 @@
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="C601">
@@ -17139,7 +17153,7 @@
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="C602">
@@ -17166,7 +17180,7 @@
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="C603">
@@ -17193,7 +17207,7 @@
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="C604">
@@ -17220,7 +17234,7 @@
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="C605">
@@ -17247,7 +17261,7 @@
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="C606">
@@ -17274,7 +17288,7 @@
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="C607">
@@ -17301,7 +17315,7 @@
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="C608">
@@ -17328,7 +17342,7 @@
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="C609">
@@ -17355,7 +17369,7 @@
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="C610">
@@ -17382,7 +17396,7 @@
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="C611">
@@ -17409,7 +17423,7 @@
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="C612">
@@ -17436,7 +17450,7 @@
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C613">
@@ -17463,7 +17477,7 @@
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C614">
@@ -17490,7 +17504,7 @@
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C615">
@@ -17517,7 +17531,7 @@
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="C616">
@@ -17544,7 +17558,7 @@
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="C617">
@@ -17571,7 +17585,7 @@
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="C618">
@@ -17598,7 +17612,7 @@
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="C619">
@@ -17625,7 +17639,7 @@
       </c>
       <c r="B620" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="C620">
@@ -17652,7 +17666,7 @@
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="C621">
@@ -17679,7 +17693,7 @@
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="C622">
@@ -17706,7 +17720,7 @@
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="C623">
@@ -17733,7 +17747,7 @@
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="C624">
@@ -17760,7 +17774,7 @@
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="C625">
@@ -17787,7 +17801,7 @@
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="C626">
@@ -17814,7 +17828,7 @@
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="C627">
@@ -17841,7 +17855,7 @@
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="C628">
@@ -17868,7 +17882,7 @@
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="C629">
@@ -17895,7 +17909,7 @@
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="C630">
@@ -17922,7 +17936,7 @@
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="C631">
@@ -17949,7 +17963,7 @@
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="C632">
@@ -17976,7 +17990,7 @@
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="C633">
@@ -18003,7 +18017,7 @@
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="C634">
@@ -18030,7 +18044,7 @@
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="C635">
@@ -18057,7 +18071,7 @@
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="C636">
@@ -18084,7 +18098,7 @@
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="C637">
@@ -18111,7 +18125,7 @@
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="C638">
@@ -18138,7 +18152,7 @@
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="C639">
@@ -18165,7 +18179,7 @@
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="C640">
@@ -18192,7 +18206,7 @@
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C641">
@@ -18219,7 +18233,7 @@
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C642">
@@ -18246,7 +18260,7 @@
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C643">
@@ -18273,7 +18287,7 @@
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="C644">
@@ -18300,7 +18314,7 @@
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="C645">
@@ -18327,7 +18341,7 @@
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="C646">
@@ -18354,7 +18368,7 @@
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="C647">
@@ -18381,7 +18395,7 @@
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="C648">
@@ -18408,7 +18422,7 @@
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="C649">
@@ -18435,7 +18449,7 @@
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="C650">
@@ -18462,7 +18476,7 @@
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="C651">
@@ -18489,7 +18503,7 @@
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="C652">
@@ -18516,7 +18530,7 @@
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="C653">
@@ -18543,7 +18557,7 @@
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="C654">
@@ -18570,7 +18584,7 @@
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="C655">
@@ -18597,7 +18611,7 @@
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="C656">
@@ -18624,7 +18638,7 @@
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="C657">
@@ -18651,7 +18665,7 @@
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="C658">
@@ -18678,7 +18692,7 @@
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="C659">
@@ -18705,7 +18719,7 @@
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="C660">
@@ -18732,7 +18746,7 @@
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="C661">
@@ -18759,7 +18773,7 @@
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="C662">
@@ -18786,7 +18800,7 @@
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="C663">
@@ -18813,7 +18827,7 @@
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="C664">
@@ -18840,7 +18854,7 @@
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="C665">
@@ -18867,7 +18881,7 @@
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="C666">
@@ -18894,7 +18908,7 @@
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="C667">
@@ -18921,7 +18935,7 @@
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="C668">
@@ -18948,7 +18962,7 @@
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C669">
@@ -18975,7 +18989,7 @@
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C670">
@@ -19002,7 +19016,7 @@
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C671">
@@ -19029,7 +19043,7 @@
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="C672">
@@ -19056,7 +19070,7 @@
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="C673">
@@ -19083,7 +19097,7 @@
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1998</t>
         </is>
       </c>
       <c r="C674">
@@ -19110,7 +19124,7 @@
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1999</t>
         </is>
       </c>
       <c r="C675">
@@ -19137,7 +19151,7 @@
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="C676">
@@ -19164,7 +19178,7 @@
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="C677">
@@ -19191,7 +19205,7 @@
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="C678">
@@ -19218,7 +19232,7 @@
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="C679">
@@ -19245,7 +19259,7 @@
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="C680">
@@ -19272,7 +19286,7 @@
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="C681">
@@ -19299,7 +19313,7 @@
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="C682">
@@ -19326,7 +19340,7 @@
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="C683">
@@ -19353,7 +19367,7 @@
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="C684">
@@ -19380,7 +19394,7 @@
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="C685">
@@ -19407,7 +19421,7 @@
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="C686">
@@ -19434,7 +19448,7 @@
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="C687">
@@ -19461,7 +19475,7 @@
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="C688">
@@ -19488,7 +19502,7 @@
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="C689">
@@ -19515,7 +19529,7 @@
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="C690">
@@ -19542,7 +19556,7 @@
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="C691">
@@ -19569,7 +19583,7 @@
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="C692">
@@ -19596,7 +19610,7 @@
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="C693">
@@ -19623,7 +19637,7 @@
       </c>
       <c r="B694" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="C694">
@@ -19650,7 +19664,7 @@
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="C695">
@@ -19677,7 +19691,7 @@
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="C696">
@@ -19704,7 +19718,7 @@
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="C697">
@@ -19731,7 +19745,7 @@
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="C698">
@@ -19758,7 +19772,7 @@
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="C699">
@@ -19785,7 +19799,7 @@
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C700">
@@ -19812,7 +19826,7 @@
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C701">
@@ -19839,7 +19853,7 @@
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C702">
@@ -19866,7 +19880,7 @@
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="C703">
@@ -19893,7 +19907,7 @@
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1999</t>
         </is>
       </c>
       <c r="C704">
@@ -19920,7 +19934,7 @@
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="C705">
@@ -19947,7 +19961,7 @@
       </c>
       <c r="B706" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="C706">
@@ -19974,7 +19988,7 @@
       </c>
       <c r="B707" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="C707">
@@ -20001,7 +20015,7 @@
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="C708">
@@ -20028,7 +20042,7 @@
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="C709">
@@ -20055,7 +20069,7 @@
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="C710">
@@ -20082,7 +20096,7 @@
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="C711">
@@ -20109,7 +20123,7 @@
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="C712">
@@ -20136,7 +20150,7 @@
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="C713">
@@ -20163,7 +20177,7 @@
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="C714">
@@ -20190,7 +20204,7 @@
       </c>
       <c r="B715" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="C715">
@@ -20217,7 +20231,7 @@
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="C716">
@@ -20244,7 +20258,7 @@
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="C717">
@@ -20271,7 +20285,7 @@
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="C718">
@@ -20298,7 +20312,7 @@
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="C719">
@@ -20325,7 +20339,7 @@
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="C720">
@@ -20352,7 +20366,7 @@
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="C721">
@@ -20379,7 +20393,7 @@
       </c>
       <c r="B722" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="C722">
@@ -20406,7 +20420,7 @@
       </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="C723">
@@ -20433,7 +20447,7 @@
       </c>
       <c r="B724" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="C724">
@@ -20460,7 +20474,7 @@
       </c>
       <c r="B725" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="C725">
@@ -20487,7 +20501,7 @@
       </c>
       <c r="B726" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="C726">
@@ -20514,7 +20528,7 @@
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="C727">
@@ -20541,7 +20555,7 @@
       </c>
       <c r="B728" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="C728">
@@ -20568,7 +20582,7 @@
       </c>
       <c r="B729" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C729">
@@ -20595,7 +20609,7 @@
       </c>
       <c r="B730" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C730">
@@ -20622,7 +20636,7 @@
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C731">
@@ -20649,7 +20663,7 @@
       </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="C732">
@@ -20676,7 +20690,7 @@
       </c>
       <c r="B733" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="C733">
@@ -20703,7 +20717,7 @@
       </c>
       <c r="B734" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="C734">
@@ -20730,7 +20744,7 @@
       </c>
       <c r="B735" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="C735">
@@ -20757,7 +20771,7 @@
       </c>
       <c r="B736" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="C736">
@@ -20784,7 +20798,7 @@
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="C737">
@@ -20811,7 +20825,7 @@
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="C738">
@@ -20838,7 +20852,7 @@
       </c>
       <c r="B739" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="C739">
@@ -20865,7 +20879,7 @@
       </c>
       <c r="B740" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="C740">
@@ -20892,7 +20906,7 @@
       </c>
       <c r="B741" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="C741">
@@ -20919,7 +20933,7 @@
       </c>
       <c r="B742" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="C742">
@@ -20946,7 +20960,7 @@
       </c>
       <c r="B743" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="C743">
@@ -20973,7 +20987,7 @@
       </c>
       <c r="B744" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="C744">
@@ -21000,7 +21014,7 @@
       </c>
       <c r="B745" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="C745">
@@ -21027,7 +21041,7 @@
       </c>
       <c r="B746" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="C746">
@@ -21054,7 +21068,7 @@
       </c>
       <c r="B747" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="C747">
@@ -21081,7 +21095,7 @@
       </c>
       <c r="B748" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="C748">
@@ -21108,7 +21122,7 @@
       </c>
       <c r="B749" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="C749">
@@ -21135,7 +21149,7 @@
       </c>
       <c r="B750" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="C750">
@@ -21162,7 +21176,7 @@
       </c>
       <c r="B751" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="C751">
@@ -21189,7 +21203,7 @@
       </c>
       <c r="B752" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="C752">
@@ -21216,7 +21230,7 @@
       </c>
       <c r="B753" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="C753">
@@ -21243,7 +21257,7 @@
       </c>
       <c r="B754" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="C754">
@@ -21270,7 +21284,7 @@
       </c>
       <c r="B755" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="C755">
@@ -21297,7 +21311,7 @@
       </c>
       <c r="B756" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="C756">
@@ -21324,7 +21338,7 @@
       </c>
       <c r="B757" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C757">
@@ -21351,7 +21365,7 @@
       </c>
       <c r="B758" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C758">
@@ -21378,7 +21392,7 @@
       </c>
       <c r="B759" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C759">
@@ -21405,7 +21419,7 @@
       </c>
       <c r="B760" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="C760">
@@ -21432,7 +21446,7 @@
       </c>
       <c r="B761" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="C761">
@@ -21459,7 +21473,7 @@
       </c>
       <c r="B762" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="C762">
@@ -21486,7 +21500,7 @@
       </c>
       <c r="B763" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="C763">
@@ -21513,7 +21527,7 @@
       </c>
       <c r="B764" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="C764">
@@ -21540,7 +21554,7 @@
       </c>
       <c r="B765" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="C765">
@@ -21567,7 +21581,7 @@
       </c>
       <c r="B766" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="C766">
@@ -21594,7 +21608,7 @@
       </c>
       <c r="B767" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="C767">
@@ -21621,7 +21635,7 @@
       </c>
       <c r="B768" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="C768">
@@ -21648,7 +21662,7 @@
       </c>
       <c r="B769" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="C769">
@@ -21675,7 +21689,7 @@
       </c>
       <c r="B770" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="C770">
@@ -21702,7 +21716,7 @@
       </c>
       <c r="B771" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="C771">
@@ -21729,7 +21743,7 @@
       </c>
       <c r="B772" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C772">
@@ -21756,7 +21770,7 @@
       </c>
       <c r="B773" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C773">
@@ -21783,7 +21797,7 @@
       </c>
       <c r="B774" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C774">
@@ -21810,7 +21824,7 @@
       </c>
       <c r="B775" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="C775">
@@ -21837,7 +21851,7 @@
       </c>
       <c r="B776" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="C776">
@@ -21864,7 +21878,7 @@
       </c>
       <c r="B777" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="C777">
@@ -21891,7 +21905,7 @@
       </c>
       <c r="B778" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="C778">
@@ -21918,7 +21932,7 @@
       </c>
       <c r="B779" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="C779">
@@ -21945,7 +21959,7 @@
       </c>
       <c r="B780" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="C780">
@@ -21972,7 +21986,7 @@
       </c>
       <c r="B781" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="C781">
@@ -21999,7 +22013,7 @@
       </c>
       <c r="B782" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="C782">
@@ -22026,7 +22040,7 @@
       </c>
       <c r="B783" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="C783">
@@ -22053,7 +22067,7 @@
       </c>
       <c r="B784" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="C784">
@@ -22080,7 +22094,7 @@
       </c>
       <c r="B785" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="C785">
@@ -22107,7 +22121,7 @@
       </c>
       <c r="B786" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="C786">
@@ -22134,7 +22148,7 @@
       </c>
       <c r="B787" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="C787">
@@ -22161,7 +22175,7 @@
       </c>
       <c r="B788" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="C788">
@@ -22188,7 +22202,7 @@
       </c>
       <c r="B789" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="C789">
@@ -22215,7 +22229,7 @@
       </c>
       <c r="B790" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="C790">
@@ -22242,7 +22256,7 @@
       </c>
       <c r="B791" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="C791">
@@ -22269,7 +22283,7 @@
       </c>
       <c r="B792" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="C792">
@@ -22296,7 +22310,7 @@
       </c>
       <c r="B793" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="C793">
@@ -22323,7 +22337,7 @@
       </c>
       <c r="B794" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C794">
@@ -22350,7 +22364,7 @@
       </c>
       <c r="B795" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C795">
@@ -22377,7 +22391,7 @@
       </c>
       <c r="B796" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C796">
@@ -22404,7 +22418,7 @@
       </c>
       <c r="B797" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="C797">
@@ -22431,7 +22445,7 @@
       </c>
       <c r="B798" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="C798">
@@ -22458,7 +22472,7 @@
       </c>
       <c r="B799" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="C799">
@@ -22485,7 +22499,7 @@
       </c>
       <c r="B800" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="C800">
@@ -22512,7 +22526,7 @@
       </c>
       <c r="B801" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="C801">
@@ -22539,7 +22553,7 @@
       </c>
       <c r="B802" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="C802">
@@ -22566,7 +22580,7 @@
       </c>
       <c r="B803" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="C803">
@@ -22593,7 +22607,7 @@
       </c>
       <c r="B804" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="C804">
@@ -22620,7 +22634,7 @@
       </c>
       <c r="B805" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="C805">
@@ -22647,7 +22661,7 @@
       </c>
       <c r="B806" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="C806">
@@ -22674,7 +22688,7 @@
       </c>
       <c r="B807" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="C807">
@@ -22701,7 +22715,7 @@
       </c>
       <c r="B808" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="C808">
@@ -22728,7 +22742,7 @@
       </c>
       <c r="B809" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="C809">
@@ -22755,7 +22769,7 @@
       </c>
       <c r="B810" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="C810">
@@ -22782,7 +22796,7 @@
       </c>
       <c r="B811" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="C811">
@@ -22809,7 +22823,7 @@
       </c>
       <c r="B812" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="C812">
@@ -22836,7 +22850,7 @@
       </c>
       <c r="B813" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="C813">
@@ -22863,7 +22877,7 @@
       </c>
       <c r="B814" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="C814">
@@ -22890,7 +22904,7 @@
       </c>
       <c r="B815" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="C815">
@@ -22917,7 +22931,7 @@
       </c>
       <c r="B816" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C816">
@@ -22944,7 +22958,7 @@
       </c>
       <c r="B817" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C817">
@@ -22971,7 +22985,7 @@
       </c>
       <c r="B818" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C818">
@@ -22998,7 +23012,7 @@
       </c>
       <c r="B819" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="C819">
@@ -23025,7 +23039,7 @@
       </c>
       <c r="B820" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="C820">
@@ -23052,7 +23066,7 @@
       </c>
       <c r="B821" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="C821">
@@ -23079,7 +23093,7 @@
       </c>
       <c r="B822" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="C822">
@@ -23106,7 +23120,7 @@
       </c>
       <c r="B823" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="C823">
@@ -23133,7 +23147,7 @@
       </c>
       <c r="B824" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="C824">
@@ -23160,7 +23174,7 @@
       </c>
       <c r="B825" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="C825">
@@ -23187,7 +23201,7 @@
       </c>
       <c r="B826" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="C826">
@@ -23214,7 +23228,7 @@
       </c>
       <c r="B827" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="C827">
@@ -23241,7 +23255,7 @@
       </c>
       <c r="B828" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="C828">
@@ -23268,7 +23282,7 @@
       </c>
       <c r="B829" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="C829">
@@ -23295,7 +23309,7 @@
       </c>
       <c r="B830" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="C830">
@@ -23322,7 +23336,7 @@
       </c>
       <c r="B831" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="C831">
@@ -23349,7 +23363,7 @@
       </c>
       <c r="B832" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="C832">
@@ -23376,7 +23390,7 @@
       </c>
       <c r="B833" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="C833">
@@ -23403,7 +23417,7 @@
       </c>
       <c r="B834" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="C834">
@@ -23430,7 +23444,7 @@
       </c>
       <c r="B835" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="C835">
@@ -23457,7 +23471,7 @@
       </c>
       <c r="B836" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="C836">
@@ -23484,7 +23498,7 @@
       </c>
       <c r="B837" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="C837">
@@ -23511,7 +23525,7 @@
       </c>
       <c r="B838" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C838">
@@ -23538,7 +23552,7 @@
       </c>
       <c r="B839" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C839">
@@ -23565,7 +23579,7 @@
       </c>
       <c r="B840" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C840">
@@ -23592,7 +23606,7 @@
       </c>
       <c r="B841" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="C841">
@@ -23619,7 +23633,7 @@
       </c>
       <c r="B842" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="C842">
@@ -23641,8 +23655,8 @@
   </sheetData>
   <autoFilter ref="A1:G1"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E842">
-      <formula1>"1,2"</formula1>
+    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E842">
+      <formula1>1</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions gridLines="1" gridLinesSet="1"/>
@@ -24066,7 +24080,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>31</v>
+        <v>2026</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -24110,8 +24124,8 @@
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E3">
-      <formula1>"1,2"</formula1>
+    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E3">
+      <formula1>1</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions gridLines="1" gridLinesSet="1"/>

--- a/tests/testthat/fixtures/example_corrupt.xlsx
+++ b/tests/testthat/fixtures/example_corrupt.xlsx
@@ -386,7 +386,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:A54"/>
+  <dimension ref="A1:A53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="100.711"/>
@@ -521,250 +521,243 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  seed              optional random seed for reproducibility</t>
+          <t xml:space="preserve">  Add optional settings as extra rows when needed, e.g. seed, warmup, cores,</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  warmup            optional warmup iterations per chain</t>
+          <t xml:space="preserve">  thin, adapt_delta, max_treedepth, df, or dose_schedule (dose ages, e.g. 1, 4).</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Leave seed/warmup blank to use the model defaults.</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>observations sheet -- one row per sampled count:</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>observations sheet -- one row per sampled count:</t>
+          <t xml:space="preserve">  Location          the location of this count (must match a Location in the locations sheet)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Location          the location of this count (must match a Location in the locations sheet)</t>
+          <t xml:space="preserve">  Observation Year  timing of the observation</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Observation Year  timing of the observation</t>
+          <t xml:space="preserve">  Youngest age      youngest age this count covers</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Youngest age      youngest age this count covers</t>
+          <t xml:space="preserve">  Oldest age        oldest age covered; for one age, repeat Youngest age or leave blank</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Oldest age        oldest age this count covers (put the same age in both for a single age)</t>
+          <t xml:space="preserve">  Dose              which dose this count is for (1 = first dose, 2 = second, ...)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Dose              which dose this count is for: 1 or 2</t>
+          <t xml:space="preserve">  Vaccinated        how many were found vaccinated</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Vaccinated        how many were found vaccinated</t>
+          <t xml:space="preserve">  Sampled           how many were sampled (Vaccinated must be &lt;= Sampled)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Sampled           how many were sampled (Vaccinated must be &lt;= Sampled)</t>
+          <t xml:space="preserve">  Censored          optional; leave blank, or put 1 for a right-censored observation</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Censored          optional; leave blank, or put 1 for a right-censored observation</t>
+          <t xml:space="preserve">  A count covering several ages is split evenly across them, and the cohort of each age</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  A count covering several ages is split evenly across them, and the cohort of each age</t>
+          <t xml:space="preserve">  is derived as Observation Year - age (a snapshot in time). If you prefer,</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  is derived as Observation Year - age (a snapshot in time). If you prefer,</t>
+          <t xml:space="preserve">  you may use a single 'Age' column instead of the two age columns.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  you may use a single 'Age' column instead of the two age columns.</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>locations sheet -- your location hierarchy, written as a tree:</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>locations sheet -- your location hierarchy, written as a tree:</t>
+          <t xml:space="preserve">  Location          a unique name for the location (you choose the names)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Location          a unique name for the location (you choose the names)</t>
+          <t xml:space="preserve">  Parent location   the name of this location's parent (must be another Location in this sheet)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Parent location   the name of this location's parent (must be another Location in this sheet)</t>
+          <t xml:space="preserve">  IMPORTANT: there must be exactly ONE root -- the single top location whose Parent location</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  IMPORTANT: there must be exactly ONE root -- the single top location whose Parent location</t>
+          <t xml:space="preserve">  is left BLANK. Every other location must name its parent, and the parents must chain up to</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  is left BLANK. Every other location must name its parent, and the parents must chain up to</t>
+          <t xml:space="preserve">  that one root (no loops, no second root). This is the most common thing to get wrong.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  that one root (no loops, no second root). This is the most common thing to get wrong.</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>target sheet -- the populations to predict coverage for (required):</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>target sheet -- the populations to predict coverage for (required):</t>
+          <t xml:space="preserve">  Location          one or more locations to predict, ';'-separated</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Location          one or more locations to predict, ';'-separated</t>
+          <t xml:space="preserve">  Target Year       timing of the target snapshot to predict</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Target Year       timing of the target snapshot to predict</t>
+          <t xml:space="preserve">  Youngest age      youngest age to predict</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Youngest age      youngest age to predict</t>
+          <t xml:space="preserve">  Oldest age        oldest age to predict</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Oldest age        oldest age to predict</t>
+          <t xml:space="preserve">  Dose              optional; leave blank to default to the final dose</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Dose              optional; leave blank to default to the final dose</t>
+          <t xml:space="preserve">  Label             optional; free-text label echoed into the results</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Label             optional; free-text label echoed into the results</t>
+          <t xml:space="preserve">  A Location-only row (year/ages/dose left blank) inherits those from the row above it.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  A Location-only row (year/ages/dose left blank) inherits those from the row above it.</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>Check from R: imuRUN::run_fit('yourfile.xlsx', dryrun = TRUE)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>Check from R: imuRUN::run_fit('yourfile.xlsx', dryrun = TRUE)</t>
+          <t>Fit from R:   imuRUN::run_fit('yourfile.xlsx')</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
-        <is>
-          <t>Fit from R:   imuRUN::run_fit('yourfile.xlsx')</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="3" t="inlineStr">
         <is>
           <t>If you installed the optional command wrapper, 'imurun yourfile.xlsx' also works.</t>
         </is>
@@ -779,12 +772,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="7.711"/>
     <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="5.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="40.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="26.711"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -835,40 +828,6 @@
       <c r="C3" t="inlineStr">
         <is>
           <t>Number of chains</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>seed</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Optional random seed for reproducibility</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>warmup</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Optional warmup iterations per chain</t>
         </is>
       </c>
     </row>
@@ -966,7 +925,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="C3">
@@ -993,7 +952,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="C4">
@@ -1020,7 +979,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="C5">
@@ -1047,7 +1006,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="C6">
@@ -1074,7 +1033,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="C7">
@@ -1101,7 +1060,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="C8">
@@ -1128,7 +1087,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="C9">
@@ -1155,7 +1114,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="C10">
@@ -1182,7 +1141,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="C11">
@@ -1209,7 +1168,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="C12">
@@ -1236,7 +1195,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="C13">
@@ -1263,7 +1222,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="C14">
@@ -1290,7 +1249,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="C15">
@@ -1317,7 +1276,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="C16">
@@ -1344,7 +1303,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="C17">
@@ -1371,7 +1330,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="C18">
@@ -1398,7 +1357,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="C19">
@@ -1425,7 +1384,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="C20">
@@ -1452,7 +1411,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="C21">
@@ -1479,7 +1438,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="C22">
@@ -1506,7 +1465,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="C23">
@@ -1533,7 +1492,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="C24">
@@ -1560,7 +1519,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C25">
@@ -1587,7 +1546,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C26">
@@ -1614,7 +1573,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C27">
@@ -1641,7 +1600,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="C28">
@@ -1668,7 +1627,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="C29">
@@ -1695,7 +1654,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="C30">
@@ -1722,7 +1681,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="C31">
@@ -1749,7 +1708,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="C32">
@@ -1776,7 +1735,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="C33">
@@ -1803,7 +1762,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="C34">
@@ -1830,7 +1789,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="C35">
@@ -1857,7 +1816,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="C36">
@@ -1884,7 +1843,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="C37">
@@ -1911,7 +1870,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="C38">
@@ -1938,7 +1897,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="C39">
@@ -1965,7 +1924,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="C40">
@@ -1992,7 +1951,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="C41">
@@ -2019,7 +1978,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="C42">
@@ -2046,7 +2005,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="C43">
@@ -2073,7 +2032,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="C44">
@@ -2100,7 +2059,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="C45">
@@ -2127,7 +2086,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="C46">
@@ -2154,7 +2113,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="C47">
@@ -2181,7 +2140,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="C48">
@@ -2208,7 +2167,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="C49">
@@ -2235,7 +2194,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="C50">
@@ -2262,7 +2221,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="C51">
@@ -2289,7 +2248,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="C52">
@@ -2316,7 +2275,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C53">
@@ -2343,7 +2302,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C54">
@@ -2370,7 +2329,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C55">
@@ -2397,7 +2356,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="C56">
@@ -2424,7 +2383,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="C57">
@@ -2451,7 +2410,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="C58">
@@ -2478,7 +2437,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="C59">
@@ -2505,7 +2464,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="C60">
@@ -2532,7 +2491,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="C61">
@@ -2559,7 +2518,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="C62">
@@ -2586,7 +2545,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="C63">
@@ -2613,7 +2572,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="C64">
@@ -2640,7 +2599,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="C65">
@@ -2667,7 +2626,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="C66">
@@ -2694,7 +2653,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="C67">
@@ -2721,7 +2680,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="C68">
@@ -2748,7 +2707,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="C69">
@@ -2775,7 +2734,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="C70">
@@ -2802,7 +2761,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="C71">
@@ -2829,7 +2788,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="C72">
@@ -2856,7 +2815,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="C73">
@@ -2883,7 +2842,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="C74">
@@ -2910,7 +2869,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="C75">
@@ -2937,7 +2896,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="C76">
@@ -2964,7 +2923,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="C77">
@@ -2991,7 +2950,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="C78">
@@ -3018,7 +2977,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="C79">
@@ -3045,7 +3004,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="C80">
@@ -3072,7 +3031,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C81">
@@ -3099,7 +3058,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C82">
@@ -3126,7 +3085,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C83">
@@ -3153,7 +3112,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="C84">
@@ -3180,7 +3139,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="C85">
@@ -3207,7 +3166,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="C86">
@@ -3234,7 +3193,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="C87">
@@ -3261,7 +3220,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="C88">
@@ -3288,7 +3247,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="C89">
@@ -3315,7 +3274,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="C90">
@@ -3342,7 +3301,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="C91">
@@ -3369,7 +3328,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="C92">
@@ -3396,7 +3355,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="C93">
@@ -3423,7 +3382,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="C94">
@@ -3450,7 +3409,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="C95">
@@ -3477,7 +3436,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="C96">
@@ -3504,7 +3463,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="C97">
@@ -3531,7 +3490,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="C98">
@@ -3558,7 +3517,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="C99">
@@ -3585,7 +3544,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="C100">
@@ -3612,7 +3571,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="C101">
@@ -3639,7 +3598,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="C102">
@@ -3666,7 +3625,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="C103">
@@ -3693,7 +3652,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="C104">
@@ -3720,7 +3679,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="C105">
@@ -3747,7 +3706,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="C106">
@@ -3774,7 +3733,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="C107">
@@ -3801,7 +3760,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="C108">
@@ -3828,7 +3787,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C109">
@@ -3855,7 +3814,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C110">
@@ -3882,7 +3841,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C111">
@@ -3909,7 +3868,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="C112">
@@ -3936,7 +3895,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="C113">
@@ -3963,7 +3922,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="C114">
@@ -3990,7 +3949,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="C115">
@@ -4017,7 +3976,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="C116">
@@ -4044,7 +4003,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="C117">
@@ -4071,7 +4030,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="C118">
@@ -4098,7 +4057,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="C119">
@@ -4125,7 +4084,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="C120">
@@ -4152,7 +4111,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="C121">
@@ -4179,7 +4138,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="C122">
@@ -4206,7 +4165,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="C123">
@@ -4233,7 +4192,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="C124">
@@ -4260,7 +4219,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="C125">
@@ -4287,7 +4246,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="C126">
@@ -4314,7 +4273,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="C127">
@@ -4341,7 +4300,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="C128">
@@ -4368,7 +4327,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="C129">
@@ -4395,7 +4354,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="C130">
@@ -4422,7 +4381,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="C131">
@@ -4449,7 +4408,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="C132">
@@ -4476,7 +4435,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="C133">
@@ -4503,7 +4462,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="C134">
@@ -4530,7 +4489,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="C135">
@@ -4557,7 +4516,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="C136">
@@ -4584,7 +4543,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C137">
@@ -4611,7 +4570,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C138">
@@ -4638,7 +4597,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C139">
@@ -4665,7 +4624,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="C140">
@@ -4692,7 +4651,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="C141">
@@ -4719,7 +4678,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="C142">
@@ -4746,7 +4705,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="C143">
@@ -4773,7 +4732,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="C144">
@@ -4800,7 +4759,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="C145">
@@ -4827,7 +4786,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="C146">
@@ -4854,7 +4813,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="C147">
@@ -4881,7 +4840,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="C148">
@@ -4908,7 +4867,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="C149">
@@ -4935,7 +4894,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="C150">
@@ -4962,7 +4921,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="C151">
@@ -4989,7 +4948,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="C152">
@@ -5016,7 +4975,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="C153">
@@ -5043,7 +5002,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="C154">
@@ -5070,7 +5029,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="C155">
@@ -5097,7 +5056,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="C156">
@@ -5124,7 +5083,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="C157">
@@ -5151,7 +5110,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="C158">
@@ -5178,7 +5137,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="C159">
@@ -5205,7 +5164,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="C160">
@@ -5232,7 +5191,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="C161">
@@ -5259,7 +5218,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="C162">
@@ -5286,7 +5245,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="C163">
@@ -5313,7 +5272,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="C164">
@@ -5340,7 +5299,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C165">
@@ -5367,7 +5326,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C166">
@@ -5394,7 +5353,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C167">
@@ -5421,7 +5380,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="C168">
@@ -5448,7 +5407,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="C169">
@@ -5475,7 +5434,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="C170">
@@ -5502,7 +5461,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="C171">
@@ -5529,7 +5488,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="C172">
@@ -5556,7 +5515,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="C173">
@@ -5583,7 +5542,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="C174">
@@ -5610,7 +5569,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="C175">
@@ -5637,7 +5596,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="C176">
@@ -5664,7 +5623,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="C177">
@@ -5691,7 +5650,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="C178">
@@ -5718,7 +5677,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="C179">
@@ -5745,7 +5704,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="C180">
@@ -5772,7 +5731,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="C181">
@@ -5799,7 +5758,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="C182">
@@ -5826,7 +5785,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="C183">
@@ -5853,7 +5812,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="C184">
@@ -5880,7 +5839,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="C185">
@@ -5907,7 +5866,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="C186">
@@ -5934,7 +5893,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="C187">
@@ -5961,7 +5920,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="C188">
@@ -5988,7 +5947,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="C189">
@@ -6015,7 +5974,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="C190">
@@ -6042,7 +6001,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="C191">
@@ -6069,7 +6028,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="C192">
@@ -6096,7 +6055,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C193">
@@ -6123,7 +6082,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C194">
@@ -6150,7 +6109,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C195">
@@ -6177,7 +6136,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="C196">
@@ -6204,7 +6163,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="C197">
@@ -6231,7 +6190,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="C198">
@@ -6258,7 +6217,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="C199">
@@ -6285,7 +6244,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="C200">
@@ -6312,7 +6271,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="C201">
@@ -6339,7 +6298,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="C202">
@@ -6366,7 +6325,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="C203">
@@ -6393,7 +6352,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="C204">
@@ -6420,7 +6379,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="C205">
@@ -6447,7 +6406,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="C206">
@@ -6474,7 +6433,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="C207">
@@ -6501,7 +6460,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="C208">
@@ -6528,7 +6487,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="C209">
@@ -6555,7 +6514,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="C210">
@@ -6582,7 +6541,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="C211">
@@ -6609,7 +6568,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="C212">
@@ -6636,7 +6595,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="C213">
@@ -6663,7 +6622,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="C214">
@@ -6690,7 +6649,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="C215">
@@ -6717,7 +6676,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="C216">
@@ -6744,7 +6703,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="C217">
@@ -6771,7 +6730,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="C218">
@@ -6798,7 +6757,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="C219">
@@ -6825,7 +6784,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="C220">
@@ -6852,7 +6811,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C221">
@@ -6879,7 +6838,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C222">
@@ -6906,7 +6865,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C223">
@@ -6933,7 +6892,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="C224">
@@ -6960,7 +6919,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="C225">
@@ -6987,7 +6946,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="C226">
@@ -7014,7 +6973,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="C227">
@@ -7041,7 +7000,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="C228">
@@ -7068,7 +7027,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="C229">
@@ -7095,7 +7054,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="C230">
@@ -7122,7 +7081,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="C231">
@@ -7149,7 +7108,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="C232">
@@ -7176,7 +7135,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="C233">
@@ -7203,7 +7162,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="C234">
@@ -7230,7 +7189,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="C235">
@@ -7257,7 +7216,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="C236">
@@ -7284,7 +7243,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="C237">
@@ -7311,7 +7270,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="C238">
@@ -7338,7 +7297,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="C239">
@@ -7365,7 +7324,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="C240">
@@ -7392,7 +7351,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="C241">
@@ -7419,7 +7378,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="C242">
@@ -7446,7 +7405,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="C243">
@@ -7473,7 +7432,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="C244">
@@ -7500,7 +7459,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="C245">
@@ -7527,7 +7486,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="C246">
@@ -7554,7 +7513,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="C247">
@@ -7581,7 +7540,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="C248">
@@ -7608,7 +7567,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C249">
@@ -7635,7 +7594,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C250">
@@ -7662,7 +7621,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C251">
@@ -7689,7 +7648,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="C252">
@@ -7716,7 +7675,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="C253">
@@ -7743,7 +7702,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="C254">
@@ -7770,7 +7729,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="C255">
@@ -7797,7 +7756,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="C256">
@@ -7824,7 +7783,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="C257">
@@ -7851,7 +7810,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="C258">
@@ -7878,7 +7837,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="C259">
@@ -7905,7 +7864,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="C260">
@@ -7932,7 +7891,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="C261">
@@ -7959,7 +7918,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="C262">
@@ -7986,7 +7945,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="C263">
@@ -8013,7 +7972,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="C264">
@@ -8040,7 +7999,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="C265">
@@ -8067,7 +8026,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="C266">
@@ -8094,7 +8053,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="C267">
@@ -8121,7 +8080,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="C268">
@@ -8148,7 +8107,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="C269">
@@ -8175,7 +8134,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="C270">
@@ -8202,7 +8161,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="C271">
@@ -8229,7 +8188,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="C272">
@@ -8256,7 +8215,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="C273">
@@ -8283,7 +8242,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="C274">
@@ -8310,7 +8269,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="C275">
@@ -8337,7 +8296,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="C276">
@@ -8364,7 +8323,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C277">
@@ -8391,7 +8350,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C278">
@@ -8418,7 +8377,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C279">
@@ -8445,7 +8404,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="C280">
@@ -8472,7 +8431,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="C281">
@@ -8499,7 +8458,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="C282">
@@ -8526,7 +8485,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="C283">
@@ -8553,7 +8512,7 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="C284">
@@ -8580,7 +8539,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="C285">
@@ -8607,7 +8566,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="C286">
@@ -8634,7 +8593,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="C287">
@@ -8661,7 +8620,7 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="C288">
@@ -8688,7 +8647,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="C289">
@@ -8715,7 +8674,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="C290">
@@ -8742,7 +8701,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="C291">
@@ -8769,7 +8728,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="C292">
@@ -8796,7 +8755,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="C293">
@@ -8823,7 +8782,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="C294">
@@ -8850,7 +8809,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="C295">
@@ -8877,7 +8836,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="C296">
@@ -8904,7 +8863,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="C297">
@@ -8931,7 +8890,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="C298">
@@ -8958,7 +8917,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="C299">
@@ -8985,7 +8944,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="C300">
@@ -9012,7 +8971,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="C301">
@@ -9039,7 +8998,7 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="C302">
@@ -9066,7 +9025,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="C303">
@@ -9093,7 +9052,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="C304">
@@ -9120,7 +9079,7 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C305">
@@ -9147,7 +9106,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C306">
@@ -9174,7 +9133,7 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C307">
@@ -9201,7 +9160,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="C308">
@@ -9228,7 +9187,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="C309">
@@ -9255,7 +9214,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="C310">
@@ -9282,7 +9241,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="C311">
@@ -9309,7 +9268,7 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="C312">
@@ -9336,7 +9295,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="C313">
@@ -9363,7 +9322,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="C314">
@@ -9390,7 +9349,7 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="C315">
@@ -9417,7 +9376,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="C316">
@@ -9444,7 +9403,7 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="C317">
@@ -9471,7 +9430,7 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="C318">
@@ -9498,7 +9457,7 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="C319">
@@ -9525,7 +9484,7 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="C320">
@@ -9552,7 +9511,7 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="C321">
@@ -9579,7 +9538,7 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="C322">
@@ -9606,7 +9565,7 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="C323">
@@ -9633,7 +9592,7 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="C324">
@@ -9660,7 +9619,7 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="C325">
@@ -9687,7 +9646,7 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="C326">
@@ -9714,7 +9673,7 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="C327">
@@ -9741,7 +9700,7 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="C328">
@@ -9768,7 +9727,7 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="C329">
@@ -9795,7 +9754,7 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="C330">
@@ -9822,7 +9781,7 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="C331">
@@ -9849,7 +9808,7 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="C332">
@@ -9876,7 +9835,7 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C333">
@@ -9903,7 +9862,7 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C334">
@@ -9930,7 +9889,7 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C335">
@@ -9957,7 +9916,7 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="C336">
@@ -9984,7 +9943,7 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="C337">
@@ -10011,7 +9970,7 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="C338">
@@ -10038,7 +9997,7 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="C339">
@@ -10065,7 +10024,7 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="C340">
@@ -10092,7 +10051,7 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="C341">
@@ -10119,7 +10078,7 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="C342">
@@ -10146,7 +10105,7 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="C343">
@@ -10173,7 +10132,7 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="C344">
@@ -10200,7 +10159,7 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="C345">
@@ -10227,7 +10186,7 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="C346">
@@ -10254,7 +10213,7 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="C347">
@@ -10281,7 +10240,7 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="C348">
@@ -10308,7 +10267,7 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="C349">
@@ -10335,7 +10294,7 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="C350">
@@ -10362,7 +10321,7 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="C351">
@@ -10389,7 +10348,7 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="C352">
@@ -10416,7 +10375,7 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="C353">
@@ -10443,7 +10402,7 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="C354">
@@ -10470,7 +10429,7 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="C355">
@@ -10497,7 +10456,7 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="C356">
@@ -10524,7 +10483,7 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="C357">
@@ -10551,7 +10510,7 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="C358">
@@ -10578,7 +10537,7 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="C359">
@@ -10605,7 +10564,7 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="C360">
@@ -10632,7 +10591,7 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C361">
@@ -10659,7 +10618,7 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C362">
@@ -10686,7 +10645,7 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C363">
@@ -10713,7 +10672,7 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="C364">
@@ -10740,7 +10699,7 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="C365">
@@ -10767,7 +10726,7 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="C366">
@@ -10794,7 +10753,7 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="C367">
@@ -10821,7 +10780,7 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="C368">
@@ -10848,7 +10807,7 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="C369">
@@ -10875,7 +10834,7 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="C370">
@@ -10902,7 +10861,7 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="C371">
@@ -10929,7 +10888,7 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="C372">
@@ -10956,7 +10915,7 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="C373">
@@ -10983,7 +10942,7 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="C374">
@@ -11010,7 +10969,7 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="C375">
@@ -11037,7 +10996,7 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="C376">
@@ -11064,7 +11023,7 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="C377">
@@ -11091,7 +11050,7 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="C378">
@@ -11118,7 +11077,7 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="C379">
@@ -11145,7 +11104,7 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="C380">
@@ -11172,7 +11131,7 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="C381">
@@ -11199,7 +11158,7 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="C382">
@@ -11226,7 +11185,7 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="C383">
@@ -11253,7 +11212,7 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="C384">
@@ -11280,7 +11239,7 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="C385">
@@ -11307,7 +11266,7 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="C386">
@@ -11334,7 +11293,7 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="C387">
@@ -11361,7 +11320,7 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="C388">
@@ -11388,7 +11347,7 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C389">
@@ -11415,7 +11374,7 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C390">
@@ -11442,7 +11401,7 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C391">
@@ -11469,7 +11428,7 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="C392">
@@ -11496,7 +11455,7 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="C393">
@@ -11523,7 +11482,7 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="C394">
@@ -11550,7 +11509,7 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="C395">
@@ -11577,7 +11536,7 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="C396">
@@ -11604,7 +11563,7 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="C397">
@@ -11631,7 +11590,7 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="C398">
@@ -11658,7 +11617,7 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="C399">
@@ -11685,7 +11644,7 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="C400">
@@ -11712,7 +11671,7 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="C401">
@@ -11739,7 +11698,7 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="C402">
@@ -11766,7 +11725,7 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="C403">
@@ -11793,7 +11752,7 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="C404">
@@ -11820,7 +11779,7 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="C405">
@@ -11847,7 +11806,7 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="C406">
@@ -11874,7 +11833,7 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="C407">
@@ -11901,7 +11860,7 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="C408">
@@ -11928,7 +11887,7 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="C409">
@@ -11955,7 +11914,7 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="C410">
@@ -11982,7 +11941,7 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="C411">
@@ -12009,7 +11968,7 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="C412">
@@ -12036,7 +11995,7 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="C413">
@@ -12063,7 +12022,7 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="C414">
@@ -12090,7 +12049,7 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="C415">
@@ -12117,7 +12076,7 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="C416">
@@ -12144,7 +12103,7 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C417">
@@ -12171,7 +12130,7 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C418">
@@ -12198,7 +12157,7 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C419">
@@ -12225,7 +12184,7 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="C420">
@@ -12252,7 +12211,7 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="C421">
@@ -12279,7 +12238,7 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="C422">
@@ -12306,7 +12265,7 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="C423">
@@ -12333,7 +12292,7 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="C424">
@@ -12360,7 +12319,7 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="C425">
@@ -12387,7 +12346,7 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="C426">
@@ -12414,7 +12373,7 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="C427">
@@ -12441,7 +12400,7 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="C428">
@@ -12468,7 +12427,7 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="C429">
@@ -12495,7 +12454,7 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="C430">
@@ -12522,7 +12481,7 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="C431">
@@ -12549,7 +12508,7 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="C432">
@@ -12576,7 +12535,7 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="C433">
@@ -12603,7 +12562,7 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="C434">
@@ -12630,7 +12589,7 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="C435">
@@ -12657,7 +12616,7 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="C436">
@@ -12684,7 +12643,7 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="C437">
@@ -12711,7 +12670,7 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="C438">
@@ -12738,7 +12697,7 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="C439">
@@ -12765,7 +12724,7 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="C440">
@@ -12792,7 +12751,7 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="C441">
@@ -12819,7 +12778,7 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="C442">
@@ -12846,7 +12805,7 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="C443">
@@ -12873,7 +12832,7 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="C444">
@@ -12900,7 +12859,7 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C445">
@@ -12927,7 +12886,7 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C446">
@@ -12954,7 +12913,7 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C447">
@@ -12981,7 +12940,7 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="C448">
@@ -13008,7 +12967,7 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="C449">
@@ -13035,7 +12994,7 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="C450">
@@ -13062,7 +13021,7 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="C451">
@@ -13089,7 +13048,7 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="C452">
@@ -13116,7 +13075,7 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="C453">
@@ -13143,7 +13102,7 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="C454">
@@ -13170,7 +13129,7 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="C455">
@@ -13197,7 +13156,7 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="C456">
@@ -13224,7 +13183,7 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="C457">
@@ -13251,7 +13210,7 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="C458">
@@ -13278,7 +13237,7 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="C459">
@@ -13305,7 +13264,7 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="C460">
@@ -13332,7 +13291,7 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="C461">
@@ -13359,7 +13318,7 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="C462">
@@ -13386,7 +13345,7 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="C463">
@@ -13413,7 +13372,7 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="C464">
@@ -13440,7 +13399,7 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="C465">
@@ -13467,7 +13426,7 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="C466">
@@ -13494,7 +13453,7 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="C467">
@@ -13521,7 +13480,7 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="C468">
@@ -13548,7 +13507,7 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="C469">
@@ -13575,7 +13534,7 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="C470">
@@ -13602,7 +13561,7 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="C471">
@@ -13629,7 +13588,7 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="C472">
@@ -13656,7 +13615,7 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C473">
@@ -13683,7 +13642,7 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C474">
@@ -13710,7 +13669,7 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C475">
@@ -13737,7 +13696,7 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="C476">
@@ -13764,7 +13723,7 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="C477">
@@ -13791,7 +13750,7 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="C478">
@@ -13818,7 +13777,7 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="C479">
@@ -13845,7 +13804,7 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="C480">
@@ -13872,7 +13831,7 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="C481">
@@ -13899,7 +13858,7 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="C482">
@@ -13926,7 +13885,7 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="C483">
@@ -13953,7 +13912,7 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="C484">
@@ -13980,7 +13939,7 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="C485">
@@ -14007,7 +13966,7 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="C486">
@@ -14034,7 +13993,7 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="C487">
@@ -14061,7 +14020,7 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="C488">
@@ -14088,7 +14047,7 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="C489">
@@ -14115,7 +14074,7 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="C490">
@@ -14142,7 +14101,7 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="C491">
@@ -14169,7 +14128,7 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="C492">
@@ -14196,7 +14155,7 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="C493">
@@ -14223,7 +14182,7 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="C494">
@@ -14250,7 +14209,7 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="C495">
@@ -14277,7 +14236,7 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="C496">
@@ -14304,7 +14263,7 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="C497">
@@ -14331,7 +14290,7 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="C498">
@@ -14358,7 +14317,7 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="C499">
@@ -14385,7 +14344,7 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="C500">
@@ -14412,7 +14371,7 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C501">
@@ -14439,7 +14398,7 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C502">
@@ -14466,7 +14425,7 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C503">
@@ -14493,7 +14452,7 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="C504">
@@ -14520,7 +14479,7 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="C505">
@@ -14547,7 +14506,7 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="C506">
@@ -14574,7 +14533,7 @@
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="C507">
@@ -14601,7 +14560,7 @@
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="C508">
@@ -14628,7 +14587,7 @@
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="C509">
@@ -14655,7 +14614,7 @@
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="C510">
@@ -14682,7 +14641,7 @@
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="C511">
@@ -14709,7 +14668,7 @@
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="C512">
@@ -14736,7 +14695,7 @@
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="C513">
@@ -14763,7 +14722,7 @@
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="C514">
@@ -14790,7 +14749,7 @@
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="C515">
@@ -14817,7 +14776,7 @@
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="C516">
@@ -14844,7 +14803,7 @@
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="C517">
@@ -14871,7 +14830,7 @@
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="C518">
@@ -14898,7 +14857,7 @@
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="C519">
@@ -14925,7 +14884,7 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="C520">
@@ -14952,7 +14911,7 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="C521">
@@ -14979,7 +14938,7 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="C522">
@@ -15006,7 +14965,7 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="C523">
@@ -15033,7 +14992,7 @@
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="C524">
@@ -15060,7 +15019,7 @@
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="C525">
@@ -15087,7 +15046,7 @@
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="C526">
@@ -15114,7 +15073,7 @@
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="C527">
@@ -15141,7 +15100,7 @@
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="C528">
@@ -15168,7 +15127,7 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C529">
@@ -15195,7 +15154,7 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C530">
@@ -15222,7 +15181,7 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C531">
@@ -15249,7 +15208,7 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="C532">
@@ -15276,7 +15235,7 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="C533">
@@ -15303,7 +15262,7 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="C534">
@@ -15330,7 +15289,7 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="C535">
@@ -15357,7 +15316,7 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="C536">
@@ -15384,7 +15343,7 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="C537">
@@ -15411,7 +15370,7 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="C538">
@@ -15438,7 +15397,7 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="C539">
@@ -15465,7 +15424,7 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="C540">
@@ -15492,7 +15451,7 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="C541">
@@ -15519,7 +15478,7 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="C542">
@@ -15546,7 +15505,7 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="C543">
@@ -15573,7 +15532,7 @@
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="C544">
@@ -15600,7 +15559,7 @@
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="C545">
@@ -15627,7 +15586,7 @@
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="C546">
@@ -15654,7 +15613,7 @@
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="C547">
@@ -15681,7 +15640,7 @@
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="C548">
@@ -15708,7 +15667,7 @@
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="C549">
@@ -15735,7 +15694,7 @@
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="C550">
@@ -15762,7 +15721,7 @@
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="C551">
@@ -15789,7 +15748,7 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="C552">
@@ -15816,7 +15775,7 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="C553">
@@ -15843,7 +15802,7 @@
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="C554">
@@ -15870,7 +15829,7 @@
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="C555">
@@ -15897,7 +15856,7 @@
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="C556">
@@ -15924,7 +15883,7 @@
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C557">
@@ -15951,7 +15910,7 @@
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C558">
@@ -15978,7 +15937,7 @@
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C559">
@@ -16005,7 +15964,7 @@
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="C560">
@@ -16032,7 +15991,7 @@
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="C561">
@@ -16059,7 +16018,7 @@
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="C562">
@@ -16086,7 +16045,7 @@
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="C563">
@@ -16113,7 +16072,7 @@
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="C564">
@@ -16140,7 +16099,7 @@
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="C565">
@@ -16167,7 +16126,7 @@
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="C566">
@@ -16194,7 +16153,7 @@
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="C567">
@@ -16221,7 +16180,7 @@
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="C568">
@@ -16248,7 +16207,7 @@
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="C569">
@@ -16275,7 +16234,7 @@
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="C570">
@@ -16302,7 +16261,7 @@
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="C571">
@@ -16329,7 +16288,7 @@
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="C572">
@@ -16356,7 +16315,7 @@
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="C573">
@@ -16383,7 +16342,7 @@
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="C574">
@@ -16410,7 +16369,7 @@
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="C575">
@@ -16437,7 +16396,7 @@
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="C576">
@@ -16464,7 +16423,7 @@
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="C577">
@@ -16491,7 +16450,7 @@
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="C578">
@@ -16518,7 +16477,7 @@
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="C579">
@@ -16545,7 +16504,7 @@
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="C580">
@@ -16572,7 +16531,7 @@
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="C581">
@@ -16599,7 +16558,7 @@
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="C582">
@@ -16626,7 +16585,7 @@
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="C583">
@@ -16653,7 +16612,7 @@
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="C584">
@@ -16680,7 +16639,7 @@
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C585">
@@ -16707,7 +16666,7 @@
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C586">
@@ -16734,7 +16693,7 @@
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C587">
@@ -16761,7 +16720,7 @@
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="C588">
@@ -16788,7 +16747,7 @@
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="C589">
@@ -16815,7 +16774,7 @@
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="C590">
@@ -16842,7 +16801,7 @@
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="C591">
@@ -16869,7 +16828,7 @@
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="C592">
@@ -16896,7 +16855,7 @@
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="C593">
@@ -16923,7 +16882,7 @@
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="C594">
@@ -16950,7 +16909,7 @@
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="C595">
@@ -16977,7 +16936,7 @@
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="C596">
@@ -17004,7 +16963,7 @@
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="C597">
@@ -17031,7 +16990,7 @@
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="C598">
@@ -17058,7 +17017,7 @@
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="C599">
@@ -17085,7 +17044,7 @@
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="C600">
@@ -17112,7 +17071,7 @@
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="C601">
@@ -17139,7 +17098,7 @@
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="C602">
@@ -17166,7 +17125,7 @@
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="C603">
@@ -17193,7 +17152,7 @@
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="C604">
@@ -17220,7 +17179,7 @@
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="C605">
@@ -17247,7 +17206,7 @@
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="C606">
@@ -17274,7 +17233,7 @@
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="C607">
@@ -17301,7 +17260,7 @@
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="C608">
@@ -17328,7 +17287,7 @@
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="C609">
@@ -17355,7 +17314,7 @@
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="C610">
@@ -17382,7 +17341,7 @@
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="C611">
@@ -17409,7 +17368,7 @@
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="C612">
@@ -17436,7 +17395,7 @@
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C613">
@@ -17463,7 +17422,7 @@
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C614">
@@ -17490,7 +17449,7 @@
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C615">
@@ -17517,7 +17476,7 @@
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="C616">
@@ -17544,7 +17503,7 @@
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="C617">
@@ -17571,7 +17530,7 @@
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="C618">
@@ -17598,7 +17557,7 @@
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="C619">
@@ -17625,7 +17584,7 @@
       </c>
       <c r="B620" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="C620">
@@ -17652,7 +17611,7 @@
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="C621">
@@ -17679,7 +17638,7 @@
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="C622">
@@ -17706,7 +17665,7 @@
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="C623">
@@ -17733,7 +17692,7 @@
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="C624">
@@ -17760,7 +17719,7 @@
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="C625">
@@ -17787,7 +17746,7 @@
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="C626">
@@ -17814,7 +17773,7 @@
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="C627">
@@ -17841,7 +17800,7 @@
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="C628">
@@ -17868,7 +17827,7 @@
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="C629">
@@ -17895,7 +17854,7 @@
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="C630">
@@ -17922,7 +17881,7 @@
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="C631">
@@ -17949,7 +17908,7 @@
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="C632">
@@ -17976,7 +17935,7 @@
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="C633">
@@ -18003,7 +17962,7 @@
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="C634">
@@ -18030,7 +17989,7 @@
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="C635">
@@ -18057,7 +18016,7 @@
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="C636">
@@ -18084,7 +18043,7 @@
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="C637">
@@ -18111,7 +18070,7 @@
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="C638">
@@ -18138,7 +18097,7 @@
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="C639">
@@ -18165,7 +18124,7 @@
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="C640">
@@ -18192,7 +18151,7 @@
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C641">
@@ -18219,7 +18178,7 @@
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C642">
@@ -18246,7 +18205,7 @@
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C643">
@@ -18273,7 +18232,7 @@
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="C644">
@@ -18300,7 +18259,7 @@
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="C645">
@@ -18327,7 +18286,7 @@
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="C646">
@@ -18354,7 +18313,7 @@
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="C647">
@@ -18381,7 +18340,7 @@
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="C648">
@@ -18408,7 +18367,7 @@
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="C649">
@@ -18435,7 +18394,7 @@
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="C650">
@@ -18462,7 +18421,7 @@
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="C651">
@@ -18489,7 +18448,7 @@
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="C652">
@@ -18516,7 +18475,7 @@
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="C653">
@@ -18543,7 +18502,7 @@
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="C654">
@@ -18570,7 +18529,7 @@
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="C655">
@@ -18597,7 +18556,7 @@
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="C656">
@@ -18624,7 +18583,7 @@
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="C657">
@@ -18651,7 +18610,7 @@
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="C658">
@@ -18678,7 +18637,7 @@
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="C659">
@@ -18705,7 +18664,7 @@
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="C660">
@@ -18732,7 +18691,7 @@
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="C661">
@@ -18759,7 +18718,7 @@
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="C662">
@@ -18786,7 +18745,7 @@
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="C663">
@@ -18813,7 +18772,7 @@
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="C664">
@@ -18840,7 +18799,7 @@
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="C665">
@@ -18867,7 +18826,7 @@
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="C666">
@@ -18894,7 +18853,7 @@
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="C667">
@@ -18921,7 +18880,7 @@
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="C668">
@@ -18948,7 +18907,7 @@
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C669">
@@ -18975,7 +18934,7 @@
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C670">
@@ -19002,7 +18961,7 @@
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C671">
@@ -19029,7 +18988,7 @@
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="C672">
@@ -19056,7 +19015,7 @@
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="C673">
@@ -19083,7 +19042,7 @@
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1998</t>
         </is>
       </c>
       <c r="C674">
@@ -19110,7 +19069,7 @@
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1999</t>
         </is>
       </c>
       <c r="C675">
@@ -19137,7 +19096,7 @@
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="C676">
@@ -19164,7 +19123,7 @@
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="C677">
@@ -19191,7 +19150,7 @@
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="C678">
@@ -19218,7 +19177,7 @@
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="C679">
@@ -19245,7 +19204,7 @@
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="C680">
@@ -19272,7 +19231,7 @@
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="C681">
@@ -19299,7 +19258,7 @@
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="C682">
@@ -19326,7 +19285,7 @@
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="C683">
@@ -19353,7 +19312,7 @@
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="C684">
@@ -19380,7 +19339,7 @@
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="C685">
@@ -19407,7 +19366,7 @@
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="C686">
@@ -19434,7 +19393,7 @@
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="C687">
@@ -19461,7 +19420,7 @@
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="C688">
@@ -19488,7 +19447,7 @@
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="C689">
@@ -19515,7 +19474,7 @@
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="C690">
@@ -19542,7 +19501,7 @@
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="C691">
@@ -19569,7 +19528,7 @@
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="C692">
@@ -19596,7 +19555,7 @@
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="C693">
@@ -19623,7 +19582,7 @@
       </c>
       <c r="B694" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="C694">
@@ -19650,7 +19609,7 @@
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="C695">
@@ -19677,7 +19636,7 @@
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="C696">
@@ -19704,7 +19663,7 @@
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="C697">
@@ -19731,7 +19690,7 @@
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="C698">
@@ -19758,7 +19717,7 @@
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="C699">
@@ -19785,7 +19744,7 @@
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C700">
@@ -19812,7 +19771,7 @@
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C701">
@@ -19839,7 +19798,7 @@
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C702">
@@ -19866,7 +19825,7 @@
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="C703">
@@ -19893,7 +19852,7 @@
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1999</t>
         </is>
       </c>
       <c r="C704">
@@ -19920,7 +19879,7 @@
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="C705">
@@ -19947,7 +19906,7 @@
       </c>
       <c r="B706" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="C706">
@@ -19974,7 +19933,7 @@
       </c>
       <c r="B707" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="C707">
@@ -20001,7 +19960,7 @@
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="C708">
@@ -20028,7 +19987,7 @@
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="C709">
@@ -20055,7 +20014,7 @@
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="C710">
@@ -20082,7 +20041,7 @@
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="C711">
@@ -20109,7 +20068,7 @@
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="C712">
@@ -20136,7 +20095,7 @@
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="C713">
@@ -20163,7 +20122,7 @@
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="C714">
@@ -20190,7 +20149,7 @@
       </c>
       <c r="B715" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="C715">
@@ -20217,7 +20176,7 @@
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="C716">
@@ -20244,7 +20203,7 @@
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="C717">
@@ -20271,7 +20230,7 @@
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="C718">
@@ -20298,7 +20257,7 @@
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="C719">
@@ -20325,7 +20284,7 @@
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="C720">
@@ -20352,7 +20311,7 @@
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="C721">
@@ -20379,7 +20338,7 @@
       </c>
       <c r="B722" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="C722">
@@ -20406,7 +20365,7 @@
       </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="C723">
@@ -20433,7 +20392,7 @@
       </c>
       <c r="B724" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="C724">
@@ -20460,7 +20419,7 @@
       </c>
       <c r="B725" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="C725">
@@ -20487,7 +20446,7 @@
       </c>
       <c r="B726" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="C726">
@@ -20514,7 +20473,7 @@
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="C727">
@@ -20541,7 +20500,7 @@
       </c>
       <c r="B728" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="C728">
@@ -20568,7 +20527,7 @@
       </c>
       <c r="B729" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C729">
@@ -20595,7 +20554,7 @@
       </c>
       <c r="B730" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C730">
@@ -20622,7 +20581,7 @@
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C731">
@@ -20649,7 +20608,7 @@
       </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="C732">
@@ -20676,7 +20635,7 @@
       </c>
       <c r="B733" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="C733">
@@ -20703,7 +20662,7 @@
       </c>
       <c r="B734" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="C734">
@@ -20730,7 +20689,7 @@
       </c>
       <c r="B735" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="C735">
@@ -20757,7 +20716,7 @@
       </c>
       <c r="B736" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="C736">
@@ -20784,7 +20743,7 @@
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="C737">
@@ -20811,7 +20770,7 @@
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="C738">
@@ -20838,7 +20797,7 @@
       </c>
       <c r="B739" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="C739">
@@ -20865,7 +20824,7 @@
       </c>
       <c r="B740" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="C740">
@@ -20892,7 +20851,7 @@
       </c>
       <c r="B741" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="C741">
@@ -20919,7 +20878,7 @@
       </c>
       <c r="B742" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="C742">
@@ -20946,7 +20905,7 @@
       </c>
       <c r="B743" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="C743">
@@ -20973,7 +20932,7 @@
       </c>
       <c r="B744" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="C744">
@@ -21000,7 +20959,7 @@
       </c>
       <c r="B745" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="C745">
@@ -21027,7 +20986,7 @@
       </c>
       <c r="B746" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="C746">
@@ -21054,7 +21013,7 @@
       </c>
       <c r="B747" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="C747">
@@ -21081,7 +21040,7 @@
       </c>
       <c r="B748" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="C748">
@@ -21108,7 +21067,7 @@
       </c>
       <c r="B749" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="C749">
@@ -21135,7 +21094,7 @@
       </c>
       <c r="B750" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="C750">
@@ -21162,7 +21121,7 @@
       </c>
       <c r="B751" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="C751">
@@ -21189,7 +21148,7 @@
       </c>
       <c r="B752" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="C752">
@@ -21216,7 +21175,7 @@
       </c>
       <c r="B753" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="C753">
@@ -21243,7 +21202,7 @@
       </c>
       <c r="B754" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="C754">
@@ -21270,7 +21229,7 @@
       </c>
       <c r="B755" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="C755">
@@ -21297,7 +21256,7 @@
       </c>
       <c r="B756" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="C756">
@@ -21324,7 +21283,7 @@
       </c>
       <c r="B757" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C757">
@@ -21351,7 +21310,7 @@
       </c>
       <c r="B758" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C758">
@@ -21378,7 +21337,7 @@
       </c>
       <c r="B759" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C759">
@@ -21405,7 +21364,7 @@
       </c>
       <c r="B760" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="C760">
@@ -21432,7 +21391,7 @@
       </c>
       <c r="B761" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="C761">
@@ -21459,7 +21418,7 @@
       </c>
       <c r="B762" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="C762">
@@ -21486,7 +21445,7 @@
       </c>
       <c r="B763" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="C763">
@@ -21513,7 +21472,7 @@
       </c>
       <c r="B764" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="C764">
@@ -21540,7 +21499,7 @@
       </c>
       <c r="B765" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="C765">
@@ -21567,7 +21526,7 @@
       </c>
       <c r="B766" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="C766">
@@ -21594,7 +21553,7 @@
       </c>
       <c r="B767" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="C767">
@@ -21621,7 +21580,7 @@
       </c>
       <c r="B768" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="C768">
@@ -21648,7 +21607,7 @@
       </c>
       <c r="B769" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="C769">
@@ -21675,7 +21634,7 @@
       </c>
       <c r="B770" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="C770">
@@ -21702,7 +21661,7 @@
       </c>
       <c r="B771" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="C771">
@@ -21729,7 +21688,7 @@
       </c>
       <c r="B772" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C772">
@@ -21756,7 +21715,7 @@
       </c>
       <c r="B773" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C773">
@@ -21783,7 +21742,7 @@
       </c>
       <c r="B774" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C774">
@@ -21810,7 +21769,7 @@
       </c>
       <c r="B775" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="C775">
@@ -21837,7 +21796,7 @@
       </c>
       <c r="B776" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="C776">
@@ -21864,7 +21823,7 @@
       </c>
       <c r="B777" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="C777">
@@ -21891,7 +21850,7 @@
       </c>
       <c r="B778" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="C778">
@@ -21918,7 +21877,7 @@
       </c>
       <c r="B779" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="C779">
@@ -21945,7 +21904,7 @@
       </c>
       <c r="B780" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="C780">
@@ -21972,7 +21931,7 @@
       </c>
       <c r="B781" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="C781">
@@ -21999,7 +21958,7 @@
       </c>
       <c r="B782" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="C782">
@@ -22026,7 +21985,7 @@
       </c>
       <c r="B783" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="C783">
@@ -22053,7 +22012,7 @@
       </c>
       <c r="B784" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="C784">
@@ -22080,7 +22039,7 @@
       </c>
       <c r="B785" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="C785">
@@ -22107,7 +22066,7 @@
       </c>
       <c r="B786" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="C786">
@@ -22134,7 +22093,7 @@
       </c>
       <c r="B787" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="C787">
@@ -22161,7 +22120,7 @@
       </c>
       <c r="B788" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="C788">
@@ -22188,7 +22147,7 @@
       </c>
       <c r="B789" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="C789">
@@ -22215,7 +22174,7 @@
       </c>
       <c r="B790" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="C790">
@@ -22242,7 +22201,7 @@
       </c>
       <c r="B791" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="C791">
@@ -22269,7 +22228,7 @@
       </c>
       <c r="B792" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="C792">
@@ -22296,7 +22255,7 @@
       </c>
       <c r="B793" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="C793">
@@ -22323,7 +22282,7 @@
       </c>
       <c r="B794" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C794">
@@ -22350,7 +22309,7 @@
       </c>
       <c r="B795" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C795">
@@ -22377,7 +22336,7 @@
       </c>
       <c r="B796" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C796">
@@ -22404,7 +22363,7 @@
       </c>
       <c r="B797" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="C797">
@@ -22431,7 +22390,7 @@
       </c>
       <c r="B798" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="C798">
@@ -22458,7 +22417,7 @@
       </c>
       <c r="B799" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="C799">
@@ -22485,7 +22444,7 @@
       </c>
       <c r="B800" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="C800">
@@ -22512,7 +22471,7 @@
       </c>
       <c r="B801" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="C801">
@@ -22539,7 +22498,7 @@
       </c>
       <c r="B802" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="C802">
@@ -22566,7 +22525,7 @@
       </c>
       <c r="B803" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="C803">
@@ -22593,7 +22552,7 @@
       </c>
       <c r="B804" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="C804">
@@ -22620,7 +22579,7 @@
       </c>
       <c r="B805" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="C805">
@@ -22647,7 +22606,7 @@
       </c>
       <c r="B806" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="C806">
@@ -22674,7 +22633,7 @@
       </c>
       <c r="B807" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="C807">
@@ -22701,7 +22660,7 @@
       </c>
       <c r="B808" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="C808">
@@ -22728,7 +22687,7 @@
       </c>
       <c r="B809" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="C809">
@@ -22755,7 +22714,7 @@
       </c>
       <c r="B810" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="C810">
@@ -22782,7 +22741,7 @@
       </c>
       <c r="B811" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="C811">
@@ -22809,7 +22768,7 @@
       </c>
       <c r="B812" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="C812">
@@ -22836,7 +22795,7 @@
       </c>
       <c r="B813" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="C813">
@@ -22863,7 +22822,7 @@
       </c>
       <c r="B814" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="C814">
@@ -22890,7 +22849,7 @@
       </c>
       <c r="B815" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="C815">
@@ -22917,7 +22876,7 @@
       </c>
       <c r="B816" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C816">
@@ -22944,7 +22903,7 @@
       </c>
       <c r="B817" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C817">
@@ -22971,7 +22930,7 @@
       </c>
       <c r="B818" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C818">
@@ -22998,7 +22957,7 @@
       </c>
       <c r="B819" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="C819">
@@ -23025,7 +22984,7 @@
       </c>
       <c r="B820" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="C820">
@@ -23052,7 +23011,7 @@
       </c>
       <c r="B821" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="C821">
@@ -23079,7 +23038,7 @@
       </c>
       <c r="B822" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="C822">
@@ -23106,7 +23065,7 @@
       </c>
       <c r="B823" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="C823">
@@ -23133,7 +23092,7 @@
       </c>
       <c r="B824" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="C824">
@@ -23160,7 +23119,7 @@
       </c>
       <c r="B825" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="C825">
@@ -23187,7 +23146,7 @@
       </c>
       <c r="B826" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="C826">
@@ -23214,7 +23173,7 @@
       </c>
       <c r="B827" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="C827">
@@ -23241,7 +23200,7 @@
       </c>
       <c r="B828" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="C828">
@@ -23268,7 +23227,7 @@
       </c>
       <c r="B829" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="C829">
@@ -23295,7 +23254,7 @@
       </c>
       <c r="B830" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="C830">
@@ -23322,7 +23281,7 @@
       </c>
       <c r="B831" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="C831">
@@ -23349,7 +23308,7 @@
       </c>
       <c r="B832" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="C832">
@@ -23376,7 +23335,7 @@
       </c>
       <c r="B833" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="C833">
@@ -23403,7 +23362,7 @@
       </c>
       <c r="B834" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="C834">
@@ -23430,7 +23389,7 @@
       </c>
       <c r="B835" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="C835">
@@ -23457,7 +23416,7 @@
       </c>
       <c r="B836" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="C836">
@@ -23484,7 +23443,7 @@
       </c>
       <c r="B837" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="C837">
@@ -23511,7 +23470,7 @@
       </c>
       <c r="B838" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C838">
@@ -23538,7 +23497,7 @@
       </c>
       <c r="B839" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C839">
@@ -23565,7 +23524,7 @@
       </c>
       <c r="B840" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C840">
@@ -23592,7 +23551,7 @@
       </c>
       <c r="B841" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="C841">
@@ -23619,7 +23578,7 @@
       </c>
       <c r="B842" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="C842">
@@ -23641,8 +23600,8 @@
   </sheetData>
   <autoFilter ref="A1:G1"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E842">
-      <formula1>"1,2"</formula1>
+    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E842">
+      <formula1>1</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions gridLines="1" gridLinesSet="1"/>
@@ -24066,7 +24025,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>31</v>
+        <v>2026</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -24110,8 +24069,8 @@
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E3">
-      <formula1>"1,2"</formula1>
+    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E3">
+      <formula1>1</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions gridLines="1" gridLinesSet="1"/>

--- a/tests/testthat/fixtures/example_corrupt.xlsx
+++ b/tests/testthat/fixtures/example_corrupt.xlsx
@@ -556,7 +556,7 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Observation Year  timing of the observation</t>
+          <t xml:space="preserve">  Observation Year  calendar year of the observation (1000-9999)</t>
         </is>
       </c>
     </row>
@@ -696,7 +696,7 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Target Year       timing of the target snapshot to predict</t>
+          <t xml:space="preserve">  Target Year       calendar year of the target snapshot (1000-9999)</t>
         </is>
       </c>
     </row>
